--- a/research/traditional_assets/database/data/germany/germany_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_oilfield_svcs_equip.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08041004605482543</v>
+        <v>0.08020031591666095</v>
       </c>
       <c r="C2">
-        <v>909.8710195317118</v>
+        <v>904.9892759900697</v>
       </c>
       <c r="D2">
-        <v>909.8710195317118</v>
+        <v>915.4182759900697</v>
       </c>
       <c r="E2">
-        <v>-263.5</v>
+        <v>-253.071</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.429</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1579,28 +1579,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5245787</v>
       </c>
       <c r="N2">
-        <v>45.53333333333333</v>
+        <v>45.00875463333333</v>
       </c>
       <c r="O2">
-        <v>13.66</v>
+        <v>13.50262639</v>
       </c>
       <c r="P2">
-        <v>31.87333333333333</v>
+        <v>31.50612824333333</v>
       </c>
       <c r="Q2">
-        <v>93.17333333333333</v>
+        <v>92.80612824333333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08041004605482543</v>
+        <v>0.08065476355218279</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751833</v>
+        <v>0.8049598972790483</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>86.79981351384137</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08020031591666095</v>
+        <v>0.07999058577849649</v>
       </c>
       <c r="C3">
-        <v>904.9892759900697</v>
+        <v>900.1755878406907</v>
       </c>
       <c r="D3">
-        <v>915.4182759900697</v>
+        <v>921.0335878406906</v>
       </c>
       <c r="E3">
-        <v>-253.071</v>
+        <v>-242.642</v>
       </c>
       <c r="F3">
-        <v>10.429</v>
+        <v>20.858</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1661,28 +1661,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M3">
-        <v>0.5245787</v>
+        <v>1.0491574</v>
       </c>
       <c r="N3">
-        <v>45.00875463333333</v>
+        <v>44.48417593333333</v>
       </c>
       <c r="O3">
-        <v>13.50262639</v>
+        <v>13.34525278</v>
       </c>
       <c r="P3">
-        <v>31.50612824333333</v>
+        <v>31.13892315333333</v>
       </c>
       <c r="Q3">
-        <v>92.80612824333333</v>
+        <v>92.43892315333333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08065476355218279</v>
+        <v>0.0809044752841801</v>
       </c>
       <c r="T3">
-        <v>0.8049598972790483</v>
+        <v>0.8107269118748288</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>86.79981351384137</v>
+        <v>43.39990675692069</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07999058577849649</v>
+        <v>0.07978085564033201</v>
       </c>
       <c r="C4">
-        <v>900.1755878406907</v>
+        <v>895.4312151990049</v>
       </c>
       <c r="D4">
-        <v>921.0335878406906</v>
+        <v>926.7182151990049</v>
       </c>
       <c r="E4">
-        <v>-242.642</v>
+        <v>-232.213</v>
       </c>
       <c r="F4">
-        <v>20.858</v>
+        <v>31.287</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1743,28 +1743,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M4">
-        <v>1.0491574</v>
+        <v>1.5737361</v>
       </c>
       <c r="N4">
-        <v>44.48417593333333</v>
+        <v>43.95959723333333</v>
       </c>
       <c r="O4">
-        <v>13.34525278</v>
+        <v>13.18787917</v>
       </c>
       <c r="P4">
-        <v>31.13892315333333</v>
+        <v>30.77171806333333</v>
       </c>
       <c r="Q4">
-        <v>92.43892315333333</v>
+        <v>92.07171806333332</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0809044752841801</v>
+        <v>0.08115933571168249</v>
       </c>
       <c r="T4">
-        <v>0.8107269118748288</v>
+        <v>0.8166128339880481</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>43.39990675692069</v>
+        <v>28.93327117128045</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07978085564033201</v>
+        <v>0.07957112550216752</v>
       </c>
       <c r="C5">
-        <v>895.4312151990049</v>
+        <v>890.7574494834163</v>
       </c>
       <c r="D5">
-        <v>926.7182151990049</v>
+        <v>932.4734494834163</v>
       </c>
       <c r="E5">
-        <v>-232.213</v>
+        <v>-221.784</v>
       </c>
       <c r="F5">
-        <v>31.287</v>
+        <v>41.716</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1825,28 +1825,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M5">
-        <v>1.5737361</v>
+        <v>2.0983148</v>
       </c>
       <c r="N5">
-        <v>43.95959723333333</v>
+        <v>43.43501853333333</v>
       </c>
       <c r="O5">
-        <v>13.18787917</v>
+        <v>13.03050556</v>
       </c>
       <c r="P5">
-        <v>30.77171806333333</v>
+        <v>30.40451297333333</v>
       </c>
       <c r="Q5">
-        <v>92.07171806333332</v>
+        <v>91.70451297333332</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08115933571168249</v>
+        <v>0.08141950573142451</v>
       </c>
       <c r="T5">
-        <v>0.8166128339880481</v>
+        <v>0.8226213794786261</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.93327117128045</v>
+        <v>21.69995337846034</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07957112550216752</v>
+        <v>0.07936139536400305</v>
       </c>
       <c r="C6">
-        <v>890.7574494834163</v>
+        <v>886.1556143933896</v>
       </c>
       <c r="D6">
-        <v>932.4734494834163</v>
+        <v>938.3006143933895</v>
       </c>
       <c r="E6">
-        <v>-221.784</v>
+        <v>-211.355</v>
       </c>
       <c r="F6">
-        <v>41.716</v>
+        <v>52.14500000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1907,28 +1907,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M6">
-        <v>2.0983148</v>
+        <v>2.6228935</v>
       </c>
       <c r="N6">
-        <v>43.43501853333333</v>
+        <v>42.91043983333333</v>
       </c>
       <c r="O6">
-        <v>13.03050556</v>
+        <v>12.87313195</v>
       </c>
       <c r="P6">
-        <v>30.40451297333333</v>
+        <v>30.03730788333333</v>
       </c>
       <c r="Q6">
-        <v>91.70451297333332</v>
+        <v>91.33730788333332</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08141950573142451</v>
+        <v>0.08168515301474005</v>
       </c>
       <c r="T6">
-        <v>0.8226213794786261</v>
+        <v>0.8287564206637427</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.69995337846034</v>
+        <v>17.35996270276827</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07936139536400305</v>
+        <v>0.07915166522583858</v>
       </c>
       <c r="C7">
-        <v>886.1556143933896</v>
+        <v>881.6270669244395</v>
       </c>
       <c r="D7">
-        <v>938.3006143933895</v>
+        <v>944.2010669244396</v>
       </c>
       <c r="E7">
-        <v>-211.355</v>
+        <v>-200.926</v>
       </c>
       <c r="F7">
-        <v>52.14500000000001</v>
+        <v>62.57400000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1989,28 +1989,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M7">
-        <v>2.6228935</v>
+        <v>3.147472200000001</v>
       </c>
       <c r="N7">
-        <v>42.91043983333333</v>
+        <v>42.38586113333333</v>
       </c>
       <c r="O7">
-        <v>12.87313195</v>
+        <v>12.71575834</v>
       </c>
       <c r="P7">
-        <v>30.03730788333333</v>
+        <v>29.67010279333333</v>
       </c>
       <c r="Q7">
-        <v>91.33730788333332</v>
+        <v>90.97010279333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08168515301474005</v>
+        <v>0.08195645236791338</v>
       </c>
       <c r="T7">
-        <v>0.8287564206637427</v>
+        <v>0.8350219946400319</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>17.35996270276827</v>
+        <v>14.46663558564022</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07915166522583858</v>
+        <v>0.07901543508767411</v>
       </c>
       <c r="C8">
-        <v>881.6270669244396</v>
+        <v>875.0706232062595</v>
       </c>
       <c r="D8">
-        <v>944.2010669244396</v>
+        <v>948.0736232062595</v>
       </c>
       <c r="E8">
-        <v>-200.926</v>
+        <v>-190.497</v>
       </c>
       <c r="F8">
-        <v>62.57400000000001</v>
+        <v>73.003</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2071,45 +2071,45 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M8">
-        <v>3.1474722</v>
+        <v>3.7815554</v>
       </c>
       <c r="N8">
-        <v>42.38586113333333</v>
+        <v>41.75177793333333</v>
       </c>
       <c r="O8">
-        <v>12.71575834</v>
+        <v>12.52553338</v>
       </c>
       <c r="P8">
-        <v>29.67010279333333</v>
+        <v>29.22624455333333</v>
       </c>
       <c r="Q8">
-        <v>90.97010279333333</v>
+        <v>90.52624455333333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08195645236791338</v>
+        <v>0.08223358611577861</v>
       </c>
       <c r="T8">
-        <v>0.8350219946400319</v>
+        <v>0.841422312142693</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.3</v>
       </c>
       <c r="W8">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.46663558564022</v>
+        <v>12.04090077150088</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0790154350876741</v>
+        <v>0.07881620494950962</v>
       </c>
       <c r="C9">
-        <v>875.0706232062598</v>
+        <v>870.3625968684458</v>
       </c>
       <c r="D9">
-        <v>948.0736232062599</v>
+        <v>953.7945968684459</v>
       </c>
       <c r="E9">
-        <v>-190.497</v>
+        <v>-180.068</v>
       </c>
       <c r="F9">
-        <v>73.00300000000001</v>
+        <v>83.432</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2153,28 +2153,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M9">
-        <v>3.781555400000001</v>
+        <v>4.3217776</v>
       </c>
       <c r="N9">
-        <v>41.75177793333333</v>
+        <v>41.21155573333333</v>
       </c>
       <c r="O9">
-        <v>12.52553338</v>
+        <v>12.36346672</v>
       </c>
       <c r="P9">
-        <v>29.22624455333333</v>
+        <v>28.84808901333334</v>
       </c>
       <c r="Q9">
-        <v>90.52624455333333</v>
+        <v>90.14808901333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08223358611577861</v>
+        <v>0.08251674451033655</v>
       </c>
       <c r="T9">
-        <v>0.841422312142693</v>
+        <v>0.8479617669823685</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>12.04090077150088</v>
+        <v>10.53578817506327</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07881620494950962</v>
+        <v>0.07872407481134516</v>
       </c>
       <c r="C10">
-        <v>870.3625968684458</v>
+        <v>862.6025626174766</v>
       </c>
       <c r="D10">
-        <v>953.7945968684459</v>
+        <v>956.4635626174766</v>
       </c>
       <c r="E10">
-        <v>-180.068</v>
+        <v>-169.639</v>
       </c>
       <c r="F10">
-        <v>83.432</v>
+        <v>93.861</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2235,45 +2235,45 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M10">
-        <v>4.3217776</v>
+        <v>5.0215635</v>
       </c>
       <c r="N10">
-        <v>41.21155573333333</v>
+        <v>40.51176983333333</v>
       </c>
       <c r="O10">
-        <v>12.36346672</v>
+        <v>12.15353095</v>
       </c>
       <c r="P10">
-        <v>28.84808901333334</v>
+        <v>28.35823888333334</v>
       </c>
       <c r="Q10">
-        <v>90.14808901333333</v>
+        <v>89.65823888333333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08251674451033655</v>
+        <v>0.08280612616631336</v>
       </c>
       <c r="T10">
-        <v>0.8479617669823685</v>
+        <v>0.8546449461042345</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.53578817506327</v>
+        <v>9.067560996357674</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07872407481134516</v>
+        <v>0.07853674467318068</v>
       </c>
       <c r="C11">
-        <v>862.6025626174766</v>
+        <v>857.6467534653501</v>
       </c>
       <c r="D11">
-        <v>956.4635626174766</v>
+        <v>961.9367534653501</v>
       </c>
       <c r="E11">
-        <v>-169.639</v>
+        <v>-159.21</v>
       </c>
       <c r="F11">
-        <v>93.861</v>
+        <v>104.29</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2317,28 +2317,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M11">
-        <v>5.0215635</v>
+        <v>5.579515000000001</v>
       </c>
       <c r="N11">
-        <v>40.51176983333333</v>
+        <v>39.95381833333333</v>
       </c>
       <c r="O11">
-        <v>12.15353095</v>
+        <v>11.9861455</v>
       </c>
       <c r="P11">
-        <v>28.35823888333334</v>
+        <v>27.96767283333333</v>
       </c>
       <c r="Q11">
-        <v>89.65823888333333</v>
+        <v>89.26767283333334</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08280612616631336</v>
+        <v>0.08310193852575631</v>
       </c>
       <c r="T11">
-        <v>0.8546449461042345</v>
+        <v>0.8614766403176976</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>9.067560996357674</v>
+        <v>8.160804896721906</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07853674467318068</v>
+        <v>0.0784110145350162</v>
       </c>
       <c r="C12">
-        <v>857.64675346535</v>
+        <v>850.926452585668</v>
       </c>
       <c r="D12">
-        <v>961.9367534653501</v>
+        <v>965.6454525856681</v>
       </c>
       <c r="E12">
-        <v>-159.21</v>
+        <v>-148.781</v>
       </c>
       <c r="F12">
-        <v>104.29</v>
+        <v>114.719</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2399,45 +2399,45 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M12">
-        <v>5.579515000000001</v>
+        <v>6.2292417</v>
       </c>
       <c r="N12">
-        <v>39.95381833333333</v>
+        <v>39.30409163333333</v>
       </c>
       <c r="O12">
-        <v>11.9861455</v>
+        <v>11.79122749</v>
       </c>
       <c r="P12">
-        <v>27.96767283333333</v>
+        <v>27.51286414333333</v>
       </c>
       <c r="Q12">
-        <v>89.26767283333334</v>
+        <v>88.81286414333333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08310193852575631</v>
+        <v>0.08340439835395079</v>
       </c>
       <c r="T12">
-        <v>0.8614766403176976</v>
+        <v>0.8684618557494408</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>8.160804896721906</v>
+        <v>7.309610948846844</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0784110145350162</v>
+        <v>0.07822928439685173</v>
       </c>
       <c r="C13">
-        <v>850.926452585668</v>
+        <v>845.908823350708</v>
       </c>
       <c r="D13">
-        <v>965.6454525856681</v>
+        <v>971.056823350708</v>
       </c>
       <c r="E13">
-        <v>-148.781</v>
+        <v>-138.352</v>
       </c>
       <c r="F13">
-        <v>114.719</v>
+        <v>125.148</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2481,28 +2481,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M13">
-        <v>6.2292417</v>
+        <v>6.7955364</v>
       </c>
       <c r="N13">
-        <v>39.30409163333333</v>
+        <v>38.73779693333333</v>
       </c>
       <c r="O13">
-        <v>11.79122749</v>
+        <v>11.62133908</v>
       </c>
       <c r="P13">
-        <v>27.51286414333333</v>
+        <v>27.11645785333333</v>
       </c>
       <c r="Q13">
-        <v>88.81286414333333</v>
+        <v>88.41645785333333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08340439835395079</v>
+        <v>0.08371373226914969</v>
       </c>
       <c r="T13">
-        <v>0.8684618557494408</v>
+        <v>0.8756058260773599</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.309610948846844</v>
+        <v>6.700476703109607</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07822928439685173</v>
+        <v>0.07804755425868724</v>
       </c>
       <c r="C14">
-        <v>845.908823350708</v>
+        <v>840.9521853555118</v>
       </c>
       <c r="D14">
-        <v>971.056823350708</v>
+        <v>976.5291853555118</v>
       </c>
       <c r="E14">
-        <v>-138.352</v>
+        <v>-127.923</v>
       </c>
       <c r="F14">
-        <v>125.148</v>
+        <v>135.577</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2563,28 +2563,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M14">
-        <v>6.7955364</v>
+        <v>7.361831100000002</v>
       </c>
       <c r="N14">
-        <v>38.73779693333333</v>
+        <v>38.17150223333333</v>
       </c>
       <c r="O14">
-        <v>11.62133908</v>
+        <v>11.45145067</v>
       </c>
       <c r="P14">
-        <v>27.11645785333333</v>
+        <v>26.72005156333333</v>
       </c>
       <c r="Q14">
-        <v>88.41645785333333</v>
+        <v>88.02005156333333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08371373226914969</v>
+        <v>0.08403017730883591</v>
       </c>
       <c r="T14">
-        <v>0.8756058260773599</v>
+        <v>0.8829140256082197</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.700476703109607</v>
+        <v>6.185055418255021</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07804755425868724</v>
+        <v>0.07796382412052277</v>
       </c>
       <c r="C15">
-        <v>840.9521853555118</v>
+        <v>833.0653247262865</v>
       </c>
       <c r="D15">
-        <v>976.5291853555118</v>
+        <v>979.0713247262864</v>
       </c>
       <c r="E15">
-        <v>-127.923</v>
+        <v>-117.494</v>
       </c>
       <c r="F15">
-        <v>135.577</v>
+        <v>146.006</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2645,45 +2645,45 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M15">
-        <v>7.361831100000002</v>
+        <v>8.074131800000002</v>
       </c>
       <c r="N15">
-        <v>38.17150223333333</v>
+        <v>37.45920153333333</v>
       </c>
       <c r="O15">
-        <v>11.45145067</v>
+        <v>11.23776046</v>
       </c>
       <c r="P15">
-        <v>26.72005156333333</v>
+        <v>26.22144107333333</v>
       </c>
       <c r="Q15">
-        <v>88.02005156333333</v>
+        <v>87.52144107333334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08403017730883591</v>
+        <v>0.08435398153549159</v>
       </c>
       <c r="T15">
-        <v>0.8829140256082197</v>
+        <v>0.8903921832677042</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.185055418255021</v>
+        <v>5.639409222095349</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07796382412052277</v>
+        <v>0.07778909398235831</v>
       </c>
       <c r="C16">
-        <v>833.0653247262865</v>
+        <v>827.9841869676064</v>
       </c>
       <c r="D16">
-        <v>979.0713247262864</v>
+        <v>984.4191869676065</v>
       </c>
       <c r="E16">
-        <v>-117.494</v>
+        <v>-107.065</v>
       </c>
       <c r="F16">
-        <v>146.006</v>
+        <v>156.435</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2727,28 +2727,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M16">
-        <v>8.074131800000002</v>
+        <v>8.650855500000002</v>
       </c>
       <c r="N16">
-        <v>37.45920153333333</v>
+        <v>36.88247783333333</v>
       </c>
       <c r="O16">
-        <v>11.23776046</v>
+        <v>11.06474335</v>
       </c>
       <c r="P16">
-        <v>26.22144107333333</v>
+        <v>25.81773448333333</v>
       </c>
       <c r="Q16">
-        <v>87.52144107333334</v>
+        <v>87.11773448333332</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08435398153549159</v>
+        <v>0.08468540468512742</v>
       </c>
       <c r="T16">
-        <v>0.8903921832677042</v>
+        <v>0.8980462975780001</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.639409222095349</v>
+        <v>5.263448607288992</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07778909398235831</v>
+        <v>0.07761436384419382</v>
       </c>
       <c r="C17">
-        <v>827.9841869676065</v>
+        <v>822.9617920279185</v>
       </c>
       <c r="D17">
-        <v>984.4191869676065</v>
+        <v>989.8257920279185</v>
       </c>
       <c r="E17">
-        <v>-107.065</v>
+        <v>-96.636</v>
       </c>
       <c r="F17">
-        <v>156.435</v>
+        <v>166.864</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2809,28 +2809,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M17">
-        <v>8.6508555</v>
+        <v>9.227579200000001</v>
       </c>
       <c r="N17">
-        <v>36.88247783333333</v>
+        <v>36.30575413333333</v>
       </c>
       <c r="O17">
-        <v>11.06474335</v>
+        <v>10.89172624</v>
       </c>
       <c r="P17">
-        <v>25.81773448333333</v>
+        <v>25.41402789333333</v>
       </c>
       <c r="Q17">
-        <v>87.11773448333332</v>
+        <v>86.71402789333334</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08468540468512742</v>
+        <v>0.0850247188621355</v>
       </c>
       <c r="T17">
-        <v>0.8980462975780001</v>
+        <v>0.9058826527052077</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.263448607288994</v>
+        <v>4.934483069333432</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07761436384419382</v>
+        <v>0.07743963370602934</v>
       </c>
       <c r="C18">
-        <v>822.9617920279185</v>
+        <v>817.9991131303287</v>
       </c>
       <c r="D18">
-        <v>989.8257920279185</v>
+        <v>995.2921131303287</v>
       </c>
       <c r="E18">
-        <v>-96.636</v>
+        <v>-86.20699999999997</v>
       </c>
       <c r="F18">
-        <v>166.864</v>
+        <v>177.293</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2891,28 +2891,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M18">
-        <v>9.227579200000001</v>
+        <v>9.804302900000001</v>
       </c>
       <c r="N18">
-        <v>36.30575413333333</v>
+        <v>35.72903043333333</v>
       </c>
       <c r="O18">
-        <v>10.89172624</v>
+        <v>10.71870913</v>
       </c>
       <c r="P18">
-        <v>25.41402789333333</v>
+        <v>25.01032130333333</v>
       </c>
       <c r="Q18">
-        <v>86.71402789333334</v>
+        <v>86.31032130333332</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0850247188621355</v>
+        <v>0.08537220928437271</v>
       </c>
       <c r="T18">
-        <v>0.9058826527052077</v>
+        <v>0.9139078356668061</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.934483069333432</v>
+        <v>4.644219359372641</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07743963370602934</v>
+        <v>0.07757990356786487</v>
       </c>
       <c r="C19">
-        <v>817.9991131303287</v>
+        <v>803.1771014619121</v>
       </c>
       <c r="D19">
-        <v>995.2921131303287</v>
+        <v>990.8991014619121</v>
       </c>
       <c r="E19">
-        <v>-86.20699999999997</v>
+        <v>-75.77799999999996</v>
       </c>
       <c r="F19">
-        <v>177.293</v>
+        <v>187.722</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2973,45 +2973,45 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M19">
-        <v>9.804302900000001</v>
+        <v>10.8503316</v>
       </c>
       <c r="N19">
-        <v>35.72903043333333</v>
+        <v>34.68300173333333</v>
       </c>
       <c r="O19">
-        <v>10.71870913</v>
+        <v>10.40490052</v>
       </c>
       <c r="P19">
-        <v>25.01032130333333</v>
+        <v>24.27810121333333</v>
       </c>
       <c r="Q19">
-        <v>86.31032130333332</v>
+        <v>85.57810121333333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08537220928437271</v>
+        <v>0.08572817508276204</v>
       </c>
       <c r="T19">
-        <v>0.9139078356668061</v>
+        <v>0.9221287547981992</v>
       </c>
       <c r="U19">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.644219359372641</v>
+        <v>4.1964923296292</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07757990356786489</v>
+        <v>0.07788817342970041</v>
       </c>
       <c r="C20">
-        <v>803.1771014619117</v>
+        <v>783.2285714777629</v>
       </c>
       <c r="D20">
-        <v>990.8991014619116</v>
+        <v>981.3795714777629</v>
       </c>
       <c r="E20">
-        <v>-75.77799999999999</v>
+        <v>-65.34899999999999</v>
       </c>
       <c r="F20">
-        <v>187.722</v>
+        <v>198.151</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -3055,45 +3055,45 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M20">
-        <v>10.8503316</v>
+        <v>12.1466563</v>
       </c>
       <c r="N20">
-        <v>34.68300173333333</v>
+        <v>33.38667703333333</v>
       </c>
       <c r="O20">
-        <v>10.40490052</v>
+        <v>10.01600311</v>
       </c>
       <c r="P20">
-        <v>24.27810121333333</v>
+        <v>23.37067392333333</v>
       </c>
       <c r="Q20">
-        <v>85.57810121333333</v>
+        <v>84.67067392333333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08572817508276204</v>
+        <v>0.08609293016012394</v>
       </c>
       <c r="T20">
-        <v>0.9221287547981992</v>
+        <v>0.9305526595871578</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.1964923296292</v>
+        <v>3.748631080747162</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07788817342970041</v>
+        <v>0.07775544329153591</v>
       </c>
       <c r="C21">
-        <v>783.2285714777629</v>
+        <v>776.8758299394487</v>
       </c>
       <c r="D21">
-        <v>981.3795714777629</v>
+        <v>985.4558299394488</v>
       </c>
       <c r="E21">
-        <v>-65.34899999999999</v>
+        <v>-54.91999999999996</v>
       </c>
       <c r="F21">
-        <v>198.151</v>
+        <v>208.58</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3137,28 +3137,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M21">
-        <v>12.1466563</v>
+        <v>12.785954</v>
       </c>
       <c r="N21">
-        <v>33.38667703333333</v>
+        <v>32.74737933333333</v>
       </c>
       <c r="O21">
-        <v>10.01600311</v>
+        <v>9.824213799999997</v>
       </c>
       <c r="P21">
-        <v>23.37067392333333</v>
+        <v>22.92316553333333</v>
       </c>
       <c r="Q21">
-        <v>84.67067392333333</v>
+        <v>84.22316553333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08609293016012394</v>
+        <v>0.0864668041144199</v>
       </c>
       <c r="T21">
-        <v>0.9305526595871578</v>
+        <v>0.9391871619958404</v>
       </c>
       <c r="U21">
         <v>0.0613</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.748631080747162</v>
+        <v>3.561199526709804</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07775544329153591</v>
+        <v>0.07803431315337145</v>
       </c>
       <c r="C22">
-        <v>776.8758299394487</v>
+        <v>757.9213208078392</v>
       </c>
       <c r="D22">
-        <v>985.4558299394488</v>
+        <v>976.9303208078392</v>
       </c>
       <c r="E22">
-        <v>-54.91999999999996</v>
+        <v>-44.49099999999996</v>
       </c>
       <c r="F22">
-        <v>208.58</v>
+        <v>219.009</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3219,45 +3219,45 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M22">
-        <v>12.785954</v>
+        <v>14.0384769</v>
       </c>
       <c r="N22">
-        <v>32.74737933333333</v>
+        <v>31.49485643333333</v>
       </c>
       <c r="O22">
-        <v>9.824213799999997</v>
+        <v>9.448456929999997</v>
       </c>
       <c r="P22">
-        <v>22.92316553333333</v>
+        <v>22.04639950333333</v>
       </c>
       <c r="Q22">
-        <v>84.22316553333333</v>
+        <v>83.34639950333332</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0864668041144199</v>
+        <v>0.08685014323211575</v>
       </c>
       <c r="T22">
-        <v>0.9391871619958404</v>
+        <v>0.9480402594022111</v>
       </c>
       <c r="U22">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.561199526709804</v>
+        <v>3.243466770482296</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07803431315337142</v>
+        <v>0.07792118301520697</v>
       </c>
       <c r="C23">
-        <v>757.9213208078399</v>
+        <v>750.9330490686177</v>
       </c>
       <c r="D23">
-        <v>976.93032080784</v>
+        <v>980.3710490686177</v>
       </c>
       <c r="E23">
-        <v>-44.49099999999999</v>
+        <v>-34.06199999999998</v>
       </c>
       <c r="F23">
-        <v>219.009</v>
+        <v>229.438</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3301,28 +3301,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M23">
-        <v>14.0384769</v>
+        <v>14.7069758</v>
       </c>
       <c r="N23">
-        <v>31.49485643333333</v>
+        <v>30.82635753333333</v>
       </c>
       <c r="O23">
-        <v>9.448456929999999</v>
+        <v>9.247907259999998</v>
       </c>
       <c r="P23">
-        <v>22.04639950333333</v>
+        <v>21.57845027333333</v>
       </c>
       <c r="Q23">
-        <v>83.34639950333333</v>
+        <v>82.87845027333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08685014323211573</v>
+        <v>0.08724331155795764</v>
       </c>
       <c r="T23">
-        <v>0.948040259402211</v>
+        <v>0.957120359306181</v>
       </c>
       <c r="U23">
         <v>0.0641</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.243466770482297</v>
+        <v>3.096036462733101</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07792118301520697</v>
+        <v>0.07906385287704248</v>
       </c>
       <c r="C24">
-        <v>750.9330490686177</v>
+        <v>706.8266378761239</v>
       </c>
       <c r="D24">
-        <v>980.3710490686177</v>
+        <v>946.6936378761238</v>
       </c>
       <c r="E24">
-        <v>-34.06199999999998</v>
+        <v>-23.63299999999998</v>
       </c>
       <c r="F24">
-        <v>229.438</v>
+        <v>239.867</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3383,45 +3383,45 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M24">
-        <v>14.7069758</v>
+        <v>17.2464373</v>
       </c>
       <c r="N24">
-        <v>30.82635753333333</v>
+        <v>28.28689603333333</v>
       </c>
       <c r="O24">
-        <v>9.247907259999998</v>
+        <v>8.486068809999997</v>
       </c>
       <c r="P24">
-        <v>21.57845027333333</v>
+        <v>19.80082722333333</v>
       </c>
       <c r="Q24">
-        <v>82.87845027333333</v>
+        <v>81.10082722333333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08724331155795764</v>
+        <v>0.08764669204810713</v>
       </c>
       <c r="T24">
-        <v>0.957120359306181</v>
+        <v>0.9664363059609035</v>
       </c>
       <c r="U24">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.096036462733101</v>
+        <v>2.640158807369063</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07906385287704248</v>
+        <v>0.079005322738878</v>
       </c>
       <c r="C25">
-        <v>706.8266378761239</v>
+        <v>698.0663495420233</v>
       </c>
       <c r="D25">
-        <v>946.6936378761238</v>
+        <v>948.3623495420234</v>
       </c>
       <c r="E25">
-        <v>-23.63299999999998</v>
+        <v>-13.20399999999995</v>
       </c>
       <c r="F25">
-        <v>239.867</v>
+        <v>250.296</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3465,28 +3465,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M25">
-        <v>17.2464373</v>
+        <v>17.99628240000001</v>
       </c>
       <c r="N25">
-        <v>28.28689603333333</v>
+        <v>27.53705093333333</v>
       </c>
       <c r="O25">
-        <v>8.486068809999997</v>
+        <v>8.261115279999997</v>
       </c>
       <c r="P25">
-        <v>19.80082722333333</v>
+        <v>19.27593565333333</v>
       </c>
       <c r="Q25">
-        <v>81.10082722333333</v>
+        <v>80.57593565333332</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08764669204810713</v>
+        <v>0.08806068781431317</v>
       </c>
       <c r="T25">
-        <v>0.9664363059609035</v>
+        <v>0.9759974091065396</v>
       </c>
       <c r="U25">
         <v>0.07190000000000001</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.640158807369063</v>
+        <v>2.530152190395352</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.079005322738878</v>
+        <v>0.07962929260071352</v>
       </c>
       <c r="C26">
-        <v>698.0663495420233</v>
+        <v>670.1451267161382</v>
       </c>
       <c r="D26">
-        <v>948.3623495420234</v>
+        <v>930.8701267161382</v>
       </c>
       <c r="E26">
-        <v>-13.20399999999998</v>
+        <v>-2.774999999999977</v>
       </c>
       <c r="F26">
-        <v>250.296</v>
+        <v>260.725</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3547,45 +3547,45 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M26">
-        <v>17.9962824</v>
+        <v>19.762955</v>
       </c>
       <c r="N26">
-        <v>27.53705093333333</v>
+        <v>25.77037833333333</v>
       </c>
       <c r="O26">
-        <v>8.261115279999999</v>
+        <v>7.731113499999998</v>
       </c>
       <c r="P26">
-        <v>19.27593565333333</v>
+        <v>18.03926483333333</v>
       </c>
       <c r="Q26">
-        <v>80.57593565333333</v>
+        <v>79.33926483333333</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08806068781431317</v>
+        <v>0.08848572346761804</v>
       </c>
       <c r="T26">
-        <v>0.9759974091065396</v>
+        <v>0.9858134750027262</v>
       </c>
       <c r="U26">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.530152190395352</v>
+        <v>2.303973941818586</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07962929260071352</v>
+        <v>0.07959806246254907</v>
       </c>
       <c r="C27">
-        <v>670.1451267161382</v>
+        <v>660.5762707762519</v>
       </c>
       <c r="D27">
-        <v>930.8701267161382</v>
+        <v>931.7302707762519</v>
       </c>
       <c r="E27">
-        <v>-2.774999999999977</v>
+        <v>7.654000000000053</v>
       </c>
       <c r="F27">
-        <v>260.725</v>
+        <v>271.1540000000001</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3629,28 +3629,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M27">
-        <v>19.762955</v>
+        <v>20.55347320000001</v>
       </c>
       <c r="N27">
-        <v>25.77037833333333</v>
+        <v>24.97986013333333</v>
       </c>
       <c r="O27">
-        <v>7.731113499999998</v>
+        <v>7.493958039999997</v>
       </c>
       <c r="P27">
-        <v>18.03926483333333</v>
+        <v>17.48590209333333</v>
       </c>
       <c r="Q27">
-        <v>79.33926483333333</v>
+        <v>78.78590209333333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08848572346761804</v>
+        <v>0.08892224657101225</v>
       </c>
       <c r="T27">
-        <v>0.9858134750027262</v>
+        <v>0.9958948399771879</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.303973941818586</v>
+        <v>2.215359559440947</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07959806246254907</v>
+        <v>0.07956683232438458</v>
       </c>
       <c r="C28">
-        <v>660.5762707762519</v>
+        <v>651.0090058898345</v>
       </c>
       <c r="D28">
-        <v>931.7302707762519</v>
+        <v>932.5920058898345</v>
       </c>
       <c r="E28">
-        <v>7.654000000000053</v>
+        <v>18.08300000000003</v>
       </c>
       <c r="F28">
-        <v>271.1540000000001</v>
+        <v>281.583</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3711,28 +3711,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M28">
-        <v>20.55347320000001</v>
+        <v>21.3439914</v>
       </c>
       <c r="N28">
-        <v>24.97986013333333</v>
+        <v>24.18934193333333</v>
       </c>
       <c r="O28">
-        <v>7.493958039999997</v>
+        <v>7.256802579999998</v>
       </c>
       <c r="P28">
-        <v>17.48590209333333</v>
+        <v>16.93253935333333</v>
       </c>
       <c r="Q28">
-        <v>78.78590209333333</v>
+        <v>78.23253935333332</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08892224657101225</v>
+        <v>0.08937072921148573</v>
       </c>
       <c r="T28">
-        <v>0.9958948399771879</v>
+        <v>1.006252406731772</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.215359559440947</v>
+        <v>2.133309205387579</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07956683232438458</v>
+        <v>0.07953560218622011</v>
       </c>
       <c r="C29">
-        <v>651.0090058898345</v>
+        <v>641.4433364755538</v>
       </c>
       <c r="D29">
-        <v>932.5920058898345</v>
+        <v>933.4553364755538</v>
       </c>
       <c r="E29">
-        <v>18.08300000000003</v>
+        <v>28.51200000000006</v>
       </c>
       <c r="F29">
-        <v>281.583</v>
+        <v>292.0120000000001</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3793,28 +3793,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M29">
-        <v>21.3439914</v>
+        <v>22.1345096</v>
       </c>
       <c r="N29">
-        <v>24.18934193333333</v>
+        <v>23.39882373333333</v>
       </c>
       <c r="O29">
-        <v>7.256802579999998</v>
+        <v>7.019647119999997</v>
       </c>
       <c r="P29">
-        <v>16.93253935333333</v>
+        <v>16.37917661333333</v>
       </c>
       <c r="Q29">
-        <v>78.23253935333332</v>
+        <v>77.67917661333333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08937072921148573</v>
+        <v>0.08983166970308348</v>
       </c>
       <c r="T29">
-        <v>1.006252406731772</v>
+        <v>1.016897683673983</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.133309205387579</v>
+        <v>2.057119590909451</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07953560218622011</v>
+        <v>0.08238697204805562</v>
       </c>
       <c r="C30">
-        <v>641.4433364755538</v>
+        <v>558.266408325064</v>
       </c>
       <c r="D30">
-        <v>933.4553364755538</v>
+        <v>860.7074083250642</v>
       </c>
       <c r="E30">
-        <v>28.51200000000006</v>
+        <v>38.94100000000009</v>
       </c>
       <c r="F30">
-        <v>292.0120000000001</v>
+        <v>302.4410000000001</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3875,45 +3875,45 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M30">
-        <v>22.1345096</v>
+        <v>27.21969000000001</v>
       </c>
       <c r="N30">
-        <v>23.39882373333333</v>
+        <v>18.31364333333332</v>
       </c>
       <c r="O30">
-        <v>7.019647119999997</v>
+        <v>5.494092999999997</v>
       </c>
       <c r="P30">
-        <v>16.37917661333333</v>
+        <v>12.81955033333333</v>
       </c>
       <c r="Q30">
-        <v>77.67917661333333</v>
+        <v>74.11955033333332</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08983166970308348</v>
+        <v>0.09030559443388117</v>
       </c>
       <c r="T30">
-        <v>1.016897683673983</v>
+        <v>1.027842827572313</v>
       </c>
       <c r="U30">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.057119590909451</v>
+        <v>1.672808666569433</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08238697204805562</v>
+        <v>0.08245514190989114</v>
       </c>
       <c r="C31">
-        <v>558.2664083250642</v>
+        <v>546.2366968818901</v>
       </c>
       <c r="D31">
-        <v>860.7074083250642</v>
+        <v>859.1066968818901</v>
       </c>
       <c r="E31">
-        <v>38.94100000000003</v>
+        <v>49.37</v>
       </c>
       <c r="F31">
-        <v>302.441</v>
+        <v>312.87</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3957,28 +3957,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M31">
-        <v>27.21969</v>
+        <v>28.1583</v>
       </c>
       <c r="N31">
-        <v>18.31364333333333</v>
+        <v>17.37503333333333</v>
       </c>
       <c r="O31">
-        <v>5.494092999999999</v>
+        <v>5.212509999999999</v>
       </c>
       <c r="P31">
-        <v>12.81955033333333</v>
+        <v>12.16252333333333</v>
       </c>
       <c r="Q31">
-        <v>74.11955033333332</v>
+        <v>73.46252333333334</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09030559443388117</v>
+        <v>0.09079305987127308</v>
       </c>
       <c r="T31">
-        <v>1.027842827572313</v>
+        <v>1.039100689867738</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.672808666569433</v>
+        <v>1.617048377683785</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08245514190989114</v>
+        <v>0.08252331177172667</v>
       </c>
       <c r="C32">
-        <v>546.2366968818901</v>
+        <v>534.2129282729895</v>
       </c>
       <c r="D32">
-        <v>859.1066968818901</v>
+        <v>857.5119282729896</v>
       </c>
       <c r="E32">
-        <v>49.37</v>
+        <v>59.79900000000004</v>
       </c>
       <c r="F32">
-        <v>312.87</v>
+        <v>323.299</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4039,28 +4039,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M32">
-        <v>28.1583</v>
+        <v>29.09691</v>
       </c>
       <c r="N32">
-        <v>17.37503333333333</v>
+        <v>16.43642333333333</v>
       </c>
       <c r="O32">
-        <v>5.212509999999999</v>
+        <v>4.930926999999999</v>
       </c>
       <c r="P32">
-        <v>12.16252333333333</v>
+        <v>11.50549633333333</v>
       </c>
       <c r="Q32">
-        <v>73.46252333333334</v>
+        <v>72.80549633333332</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09079305987127308</v>
+        <v>0.09129465474163287</v>
       </c>
       <c r="T32">
-        <v>1.039100689867738</v>
+        <v>1.050684867012306</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.617048377683785</v>
+        <v>1.56488552679076</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08252331177172667</v>
+        <v>0.0825914816335622</v>
       </c>
       <c r="C33">
-        <v>534.2129282729895</v>
+        <v>522.1950694644506</v>
       </c>
       <c r="D33">
-        <v>857.5119282729896</v>
+        <v>855.9230694644507</v>
       </c>
       <c r="E33">
-        <v>59.79900000000004</v>
+        <v>70.22800000000001</v>
       </c>
       <c r="F33">
-        <v>323.299</v>
+        <v>333.728</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4121,28 +4121,28 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M33">
-        <v>29.09691</v>
+        <v>30.03552</v>
       </c>
       <c r="N33">
-        <v>16.43642333333333</v>
+        <v>15.49781333333333</v>
       </c>
       <c r="O33">
-        <v>4.930926999999999</v>
+        <v>4.649344</v>
       </c>
       <c r="P33">
-        <v>11.50549633333333</v>
+        <v>10.84846933333333</v>
       </c>
       <c r="Q33">
-        <v>72.80549633333332</v>
+        <v>72.14846933333334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09129465474163287</v>
+        <v>0.09181100240229736</v>
       </c>
       <c r="T33">
-        <v>1.050684867012306</v>
+        <v>1.062609755249361</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.56488552679076</v>
+        <v>1.515982854078549</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0825914816335622</v>
+        <v>0.09755390540486075</v>
       </c>
       <c r="C34">
-        <v>522.1950694644506</v>
+        <v>264.3125955522208</v>
       </c>
       <c r="D34">
-        <v>855.9230694644507</v>
+        <v>608.4695955522209</v>
       </c>
       <c r="E34">
-        <v>70.22800000000001</v>
+        <v>80.65700000000004</v>
       </c>
       <c r="F34">
-        <v>333.728</v>
+        <v>344.157</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4203,45 +4203,45 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M34">
-        <v>30.03552</v>
+        <v>50.52224760000001</v>
       </c>
       <c r="N34">
-        <v>15.49781333333333</v>
+        <v>-4.988914266666676</v>
       </c>
       <c r="O34">
-        <v>4.649344</v>
+        <v>-1.496674280000003</v>
       </c>
       <c r="P34">
-        <v>10.84846933333333</v>
+        <v>-3.492239986666673</v>
       </c>
       <c r="Q34">
-        <v>72.14846933333334</v>
+        <v>57.80776001333332</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09181100240229736</v>
+        <v>0.09284775711059612</v>
       </c>
       <c r="T34">
-        <v>1.062609755249361</v>
+        <v>1.08655328199991</v>
       </c>
       <c r="U34">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.3</v>
+        <v>0.2703759363231495</v>
       </c>
       <c r="W34">
-        <v>0.063</v>
+        <v>0.1071088125477617</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y34">
-        <v>1.515982854078549</v>
+        <v>0.9012531210771653</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09755390540486075</v>
+        <v>0.09856390540486074</v>
       </c>
       <c r="C35">
-        <v>264.3125955522208</v>
+        <v>242.2363475558448</v>
       </c>
       <c r="D35">
-        <v>608.4695955522209</v>
+        <v>596.8223475558449</v>
       </c>
       <c r="E35">
-        <v>80.65700000000004</v>
+        <v>91.08600000000007</v>
       </c>
       <c r="F35">
-        <v>344.157</v>
+        <v>354.5860000000001</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4285,37 +4285,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M35">
-        <v>50.52224760000001</v>
+        <v>52.05322480000002</v>
       </c>
       <c r="N35">
-        <v>-4.988914266666676</v>
+        <v>-6.519891466666685</v>
       </c>
       <c r="O35">
-        <v>-1.496674280000003</v>
+        <v>-1.955967440000006</v>
       </c>
       <c r="P35">
-        <v>-3.492239986666673</v>
+        <v>-4.56392402666668</v>
       </c>
       <c r="Q35">
-        <v>57.80776001333332</v>
+        <v>56.73607597333331</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09284775711059612</v>
+        <v>0.09356060191530212</v>
       </c>
       <c r="T35">
-        <v>1.08655328199991</v>
+        <v>1.10301621051506</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.2703759363231495</v>
+        <v>0.2624237029018804</v>
       </c>
       <c r="W35">
-        <v>0.1071088125477617</v>
+        <v>0.108276200414004</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.9012531210771653</v>
+        <v>0.8747456763396015</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09856390540486074</v>
+        <v>0.09957390540486075</v>
       </c>
       <c r="C36">
-        <v>242.2363475558448</v>
+        <v>220.5976248010433</v>
       </c>
       <c r="D36">
-        <v>596.8223475558449</v>
+        <v>585.6126248010434</v>
       </c>
       <c r="E36">
-        <v>91.08600000000007</v>
+        <v>101.515</v>
       </c>
       <c r="F36">
-        <v>354.5860000000001</v>
+        <v>365.015</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4367,37 +4367,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M36">
-        <v>52.05322480000002</v>
+        <v>53.58420200000001</v>
       </c>
       <c r="N36">
-        <v>-6.519891466666685</v>
+        <v>-8.05086866666668</v>
       </c>
       <c r="O36">
-        <v>-1.955967440000006</v>
+        <v>-2.415260600000004</v>
       </c>
       <c r="P36">
-        <v>-4.56392402666668</v>
+        <v>-5.635608066666677</v>
       </c>
       <c r="Q36">
-        <v>56.73607597333331</v>
+        <v>55.66439193333332</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09356060191530212</v>
+        <v>0.09429538040630676</v>
       </c>
       <c r="T36">
-        <v>1.10301621051506</v>
+        <v>1.11998569067683</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.2624237029018804</v>
+        <v>0.2549258828189696</v>
       </c>
       <c r="W36">
-        <v>0.108276200414004</v>
+        <v>0.1093768804021753</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8747456763396015</v>
+        <v>0.8497529427298987</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09957390540486075</v>
+        <v>0.1005839054048607</v>
       </c>
       <c r="C37">
-        <v>220.5976248010433</v>
+        <v>199.372228547837</v>
       </c>
       <c r="D37">
-        <v>585.6126248010434</v>
+        <v>574.8162285478371</v>
       </c>
       <c r="E37">
-        <v>101.515</v>
+        <v>111.9440000000001</v>
       </c>
       <c r="F37">
-        <v>365.015</v>
+        <v>375.4440000000001</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4449,37 +4449,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M37">
-        <v>53.58420200000001</v>
+        <v>55.11517920000001</v>
       </c>
       <c r="N37">
-        <v>-8.05086866666668</v>
+        <v>-9.581845866666683</v>
       </c>
       <c r="O37">
-        <v>-2.415260600000004</v>
+        <v>-2.874553760000005</v>
       </c>
       <c r="P37">
-        <v>-5.635608066666677</v>
+        <v>-6.707292106666678</v>
       </c>
       <c r="Q37">
-        <v>55.66439193333332</v>
+        <v>54.59270789333332</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09429538040630676</v>
+        <v>0.0950531207251553</v>
       </c>
       <c r="T37">
-        <v>1.11998569067683</v>
+        <v>1.137485467093656</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.2549258828189696</v>
+        <v>0.2478446082962204</v>
       </c>
       <c r="W37">
-        <v>0.1093768804021753</v>
+        <v>0.1104164115021148</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8497529427298987</v>
+        <v>0.8261486943207348</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1005839054048607</v>
+        <v>0.1015939054048607</v>
       </c>
       <c r="C38">
-        <v>199.3722285478371</v>
+        <v>178.5377122710945</v>
       </c>
       <c r="D38">
-        <v>574.8162285478371</v>
+        <v>564.4107122710946</v>
       </c>
       <c r="E38">
-        <v>111.944</v>
+        <v>122.373</v>
       </c>
       <c r="F38">
-        <v>375.444</v>
+        <v>385.873</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4531,37 +4531,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M38">
-        <v>55.11517920000001</v>
+        <v>56.64615640000001</v>
       </c>
       <c r="N38">
-        <v>-9.581845866666676</v>
+        <v>-11.11282306666668</v>
       </c>
       <c r="O38">
-        <v>-2.874553760000003</v>
+        <v>-3.333846920000003</v>
       </c>
       <c r="P38">
-        <v>-6.707292106666673</v>
+        <v>-7.778976146666675</v>
       </c>
       <c r="Q38">
-        <v>54.59270789333333</v>
+        <v>53.52102385333332</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0950531207251553</v>
+        <v>0.09583491629222127</v>
       </c>
       <c r="T38">
-        <v>1.137485467093656</v>
+        <v>1.155540791968158</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.2478446082962205</v>
+        <v>0.2411461053692956</v>
       </c>
       <c r="W38">
-        <v>0.1104164115021148</v>
+        <v>0.1113997517317874</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8261486943207349</v>
+        <v>0.8038203512309853</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1015939054048607</v>
+        <v>0.1239543567728847</v>
       </c>
       <c r="C39">
-        <v>178.5377122710945</v>
+        <v>6.627269592160076</v>
       </c>
       <c r="D39">
-        <v>564.4107122710946</v>
+        <v>402.9292695921601</v>
       </c>
       <c r="E39">
-        <v>122.373</v>
+        <v>132.802</v>
       </c>
       <c r="F39">
-        <v>385.873</v>
+        <v>396.302</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4613,45 +4613,45 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M39">
-        <v>56.64615640000001</v>
+        <v>79.5774416</v>
       </c>
       <c r="N39">
-        <v>-11.11282306666668</v>
+        <v>-34.04410826666667</v>
       </c>
       <c r="O39">
-        <v>-3.333846920000003</v>
+        <v>-10.21323248</v>
       </c>
       <c r="P39">
-        <v>-7.778976146666675</v>
+        <v>-23.83087578666667</v>
       </c>
       <c r="Q39">
-        <v>53.52102385333332</v>
+        <v>37.46912421333333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09583491629222127</v>
+        <v>0.09798136876148925</v>
       </c>
       <c r="T39">
-        <v>1.155540791968158</v>
+        <v>1.20511244252862</v>
       </c>
       <c r="U39">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.2411461053692956</v>
+        <v>0.1716566871885964</v>
       </c>
       <c r="W39">
-        <v>0.1113997517317874</v>
+        <v>0.1663313372125299</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.8038203512309853</v>
+        <v>0.5721889572953214</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1239543567728847</v>
+        <v>0.1255043567728847</v>
       </c>
       <c r="C40">
-        <v>6.627269592160076</v>
+        <v>-11.63744219518253</v>
       </c>
       <c r="D40">
-        <v>402.9292695921601</v>
+        <v>395.0935578048175</v>
       </c>
       <c r="E40">
-        <v>132.802</v>
+        <v>143.2310000000001</v>
       </c>
       <c r="F40">
-        <v>396.302</v>
+        <v>406.7310000000001</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4695,37 +4695,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M40">
-        <v>79.5774416</v>
+        <v>81.67158480000002</v>
       </c>
       <c r="N40">
-        <v>-34.04410826666667</v>
+        <v>-36.13825146666669</v>
       </c>
       <c r="O40">
-        <v>-10.21323248</v>
+        <v>-10.84147544000001</v>
       </c>
       <c r="P40">
-        <v>-23.83087578666667</v>
+        <v>-25.29677602666668</v>
       </c>
       <c r="Q40">
-        <v>37.46912421333333</v>
+        <v>36.00322397333331</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09798136876148925</v>
+        <v>0.09883680103626775</v>
       </c>
       <c r="T40">
-        <v>1.20511244252862</v>
+        <v>1.224868384209417</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1716566871885964</v>
+        <v>0.1672552336709401</v>
       </c>
       <c r="W40">
-        <v>0.1663313372125299</v>
+        <v>0.1672151490788752</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5721889572953214</v>
+        <v>0.5575174455698002</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1255043567728847</v>
+        <v>0.1270543567728847</v>
       </c>
       <c r="C41">
-        <v>-11.63744219518253</v>
+        <v>-29.60320747054112</v>
       </c>
       <c r="D41">
-        <v>395.0935578048175</v>
+        <v>387.556792529459</v>
       </c>
       <c r="E41">
-        <v>143.2310000000001</v>
+        <v>153.6600000000001</v>
       </c>
       <c r="F41">
-        <v>406.7310000000001</v>
+        <v>417.1600000000001</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4777,37 +4777,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M41">
-        <v>81.67158480000002</v>
+        <v>83.76572800000002</v>
       </c>
       <c r="N41">
-        <v>-36.13825146666669</v>
+        <v>-38.23239466666669</v>
       </c>
       <c r="O41">
-        <v>-10.84147544000001</v>
+        <v>-11.46971840000001</v>
       </c>
       <c r="P41">
-        <v>-25.29677602666668</v>
+        <v>-26.76267626666669</v>
       </c>
       <c r="Q41">
-        <v>36.00322397333331</v>
+        <v>34.53732373333331</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09883680103626775</v>
+        <v>0.09972074772020556</v>
       </c>
       <c r="T41">
-        <v>1.224868384209417</v>
+        <v>1.245282857279574</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1672552336709401</v>
+        <v>0.1630738528291665</v>
       </c>
       <c r="W41">
-        <v>0.1672151490788752</v>
+        <v>0.1680547703519034</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5575174455698002</v>
+        <v>0.5435795094305551</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1270543567728847</v>
+        <v>0.1286043567728847</v>
       </c>
       <c r="C42">
-        <v>-29.60320747054112</v>
+        <v>-47.28681401338622</v>
       </c>
       <c r="D42">
-        <v>387.556792529459</v>
+        <v>380.3021859866138</v>
       </c>
       <c r="E42">
-        <v>153.6600000000001</v>
+        <v>164.0890000000001</v>
       </c>
       <c r="F42">
-        <v>417.1600000000001</v>
+        <v>427.5890000000001</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4859,37 +4859,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M42">
-        <v>83.76572800000002</v>
+        <v>85.85987120000001</v>
       </c>
       <c r="N42">
-        <v>-38.23239466666669</v>
+        <v>-40.32653786666668</v>
       </c>
       <c r="O42">
-        <v>-11.46971840000001</v>
+        <v>-12.09796136</v>
       </c>
       <c r="P42">
-        <v>-26.76267626666669</v>
+        <v>-28.22857650666668</v>
       </c>
       <c r="Q42">
-        <v>34.53732373333331</v>
+        <v>33.07142349333332</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09972074772020556</v>
+        <v>0.1006346586985141</v>
       </c>
       <c r="T42">
-        <v>1.245282857279574</v>
+        <v>1.266389346386007</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1630738528291665</v>
+        <v>0.1590964417845527</v>
       </c>
       <c r="W42">
-        <v>0.1680547703519034</v>
+        <v>0.1688534344896618</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5435795094305551</v>
+        <v>0.5303214726151758</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1286043567728847</v>
+        <v>0.1301543567728847</v>
       </c>
       <c r="C43">
-        <v>-47.28681401338622</v>
+        <v>-64.70381571039798</v>
       </c>
       <c r="D43">
-        <v>380.3021859866138</v>
+        <v>373.3141842896021</v>
       </c>
       <c r="E43">
-        <v>164.0890000000001</v>
+        <v>174.5180000000001</v>
       </c>
       <c r="F43">
-        <v>427.5890000000001</v>
+        <v>438.0180000000001</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4941,37 +4941,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M43">
-        <v>85.85987120000001</v>
+        <v>87.95401440000002</v>
       </c>
       <c r="N43">
-        <v>-40.32653786666668</v>
+        <v>-42.42068106666669</v>
       </c>
       <c r="O43">
-        <v>-12.09796136</v>
+        <v>-12.72620432000001</v>
       </c>
       <c r="P43">
-        <v>-28.22857650666668</v>
+        <v>-29.69447674666668</v>
       </c>
       <c r="Q43">
-        <v>33.07142349333332</v>
+        <v>31.60552325333332</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1006346586985141</v>
+        <v>0.1015800838484885</v>
       </c>
       <c r="T43">
-        <v>1.266389346386007</v>
+        <v>1.288223645461628</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1590964417845527</v>
+        <v>0.1553084312658729</v>
       </c>
       <c r="W43">
-        <v>0.1688534344896618</v>
+        <v>0.1696140670018127</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5303214726151758</v>
+        <v>0.517694770886243</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1301543567728847</v>
+        <v>0.1317043567728847</v>
       </c>
       <c r="C44">
-        <v>-64.70381571039792</v>
+        <v>-81.86864387309168</v>
       </c>
       <c r="D44">
-        <v>373.3141842896021</v>
+        <v>366.5783561269084</v>
       </c>
       <c r="E44">
-        <v>174.518</v>
+        <v>184.9470000000001</v>
       </c>
       <c r="F44">
-        <v>438.018</v>
+        <v>448.4470000000001</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -5023,37 +5023,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M44">
-        <v>87.95401440000001</v>
+        <v>90.04815760000001</v>
       </c>
       <c r="N44">
-        <v>-42.42068106666667</v>
+        <v>-44.51482426666668</v>
       </c>
       <c r="O44">
-        <v>-12.72620432</v>
+        <v>-13.35444728</v>
       </c>
       <c r="P44">
-        <v>-29.69447674666667</v>
+        <v>-31.16037698666668</v>
       </c>
       <c r="Q44">
-        <v>31.60552325333332</v>
+        <v>30.13962301333332</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1015800838484885</v>
+        <v>0.1025586818107427</v>
       </c>
       <c r="T44">
-        <v>1.288223645461628</v>
+        <v>1.310824060294288</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1553084312658729</v>
+        <v>0.1516966072829457</v>
       </c>
       <c r="W44">
-        <v>0.1696140670018127</v>
+        <v>0.1703393212575845</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5176947708862432</v>
+        <v>0.5056553576098188</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1317043567728847</v>
+        <v>0.1489894539306225</v>
       </c>
       <c r="C45">
-        <v>-81.86864387309168</v>
+        <v>-153.7025865316461</v>
       </c>
       <c r="D45">
-        <v>366.5783561269084</v>
+        <v>305.1734134683539</v>
       </c>
       <c r="E45">
-        <v>184.9470000000001</v>
+        <v>195.376</v>
       </c>
       <c r="F45">
-        <v>448.4470000000001</v>
+        <v>458.876</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -5105,45 +5105,45 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M45">
-        <v>90.04815760000001</v>
+        <v>108.2029608</v>
       </c>
       <c r="N45">
-        <v>-44.51482426666668</v>
+        <v>-62.66962746666668</v>
       </c>
       <c r="O45">
-        <v>-13.35444728</v>
+        <v>-18.80088824</v>
       </c>
       <c r="P45">
-        <v>-31.16037698666668</v>
+        <v>-43.86873922666668</v>
       </c>
       <c r="Q45">
-        <v>30.13962301333332</v>
+        <v>17.43126077333332</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1025586818107427</v>
+        <v>0.1041706174818949</v>
       </c>
       <c r="T45">
-        <v>1.310824060294288</v>
+        <v>1.348051212052999</v>
       </c>
       <c r="U45">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.1516966072829457</v>
+        <v>0.126244234898977</v>
       </c>
       <c r="W45">
-        <v>0.1703393212575845</v>
+        <v>0.2060316094108212</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.5056553576098188</v>
+        <v>0.4208141163299233</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1489894539306225</v>
+        <v>0.1508894539306225</v>
       </c>
       <c r="C46">
-        <v>-153.7025865316461</v>
+        <v>-169.6490715304041</v>
       </c>
       <c r="D46">
-        <v>305.1734134683539</v>
+        <v>299.6559284695959</v>
       </c>
       <c r="E46">
-        <v>195.376</v>
+        <v>205.8050000000001</v>
       </c>
       <c r="F46">
-        <v>458.876</v>
+        <v>469.3050000000001</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5187,37 +5187,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M46">
-        <v>108.2029608</v>
+        <v>110.662119</v>
       </c>
       <c r="N46">
-        <v>-62.66962746666668</v>
+        <v>-65.12878566666669</v>
       </c>
       <c r="O46">
-        <v>-18.80088824</v>
+        <v>-19.5386357</v>
       </c>
       <c r="P46">
-        <v>-43.86873922666668</v>
+        <v>-45.59014996666669</v>
       </c>
       <c r="Q46">
-        <v>17.43126077333332</v>
+        <v>15.70985003333331</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1041706174818949</v>
+        <v>0.1052319014361111</v>
       </c>
       <c r="T46">
-        <v>1.348051212052999</v>
+        <v>1.372561234090327</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.126244234898977</v>
+        <v>0.1234388074567775</v>
       </c>
       <c r="W46">
-        <v>0.2060316094108212</v>
+        <v>0.2066931292016919</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4208141163299233</v>
+        <v>0.4114626915225916</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1508894539306225</v>
+        <v>0.1527894539306225</v>
       </c>
       <c r="C47">
-        <v>-169.6490715304041</v>
+        <v>-185.399589148967</v>
       </c>
       <c r="D47">
-        <v>299.6559284695959</v>
+        <v>294.334410851033</v>
       </c>
       <c r="E47">
-        <v>205.8050000000001</v>
+        <v>216.234</v>
       </c>
       <c r="F47">
-        <v>469.3050000000001</v>
+        <v>479.734</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5269,37 +5269,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M47">
-        <v>110.662119</v>
+        <v>113.1212772</v>
       </c>
       <c r="N47">
-        <v>-65.12878566666669</v>
+        <v>-67.58794386666668</v>
       </c>
       <c r="O47">
-        <v>-19.5386357</v>
+        <v>-20.27638316</v>
       </c>
       <c r="P47">
-        <v>-45.59014996666669</v>
+        <v>-47.31156070666668</v>
       </c>
       <c r="Q47">
-        <v>15.70985003333331</v>
+        <v>13.98843929333332</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1052319014361111</v>
+        <v>0.1063324922034465</v>
       </c>
       <c r="T47">
-        <v>1.372561234090327</v>
+        <v>1.397979034721629</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.1234388074567775</v>
+        <v>0.1207553551207606</v>
       </c>
       <c r="W47">
-        <v>0.2066931292016919</v>
+        <v>0.2073258872625247</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4114626915225916</v>
+        <v>0.4025178504025353</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1527894539306225</v>
+        <v>0.1546894539306225</v>
       </c>
       <c r="C48">
-        <v>-185.399589148967</v>
+        <v>-200.9643976265563</v>
       </c>
       <c r="D48">
-        <v>294.334410851033</v>
+        <v>289.1986023734437</v>
       </c>
       <c r="E48">
-        <v>216.234</v>
+        <v>226.6630000000001</v>
       </c>
       <c r="F48">
-        <v>479.734</v>
+        <v>490.1630000000001</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5351,37 +5351,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M48">
-        <v>113.1212772</v>
+        <v>115.5804354</v>
       </c>
       <c r="N48">
-        <v>-67.58794386666668</v>
+        <v>-70.0471020666667</v>
       </c>
       <c r="O48">
-        <v>-20.27638316</v>
+        <v>-21.01413062000001</v>
       </c>
       <c r="P48">
-        <v>-47.31156070666668</v>
+        <v>-49.03297144666669</v>
       </c>
       <c r="Q48">
-        <v>13.98843929333332</v>
+        <v>12.2670285533333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1063324922034465</v>
+        <v>0.1074746146978512</v>
       </c>
       <c r="T48">
-        <v>1.397979034721629</v>
+        <v>1.424355997640905</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.1207553551207606</v>
+        <v>0.1181860922458508</v>
       </c>
       <c r="W48">
-        <v>0.2073258872625247</v>
+        <v>0.2079317194484284</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4025178504025353</v>
+        <v>0.3939536408195026</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1546894539306225</v>
+        <v>0.1565894539306225</v>
       </c>
       <c r="C49">
-        <v>-200.9643976265563</v>
+        <v>-216.3530515016773</v>
       </c>
       <c r="D49">
-        <v>289.1986023734437</v>
+        <v>284.2389484983228</v>
       </c>
       <c r="E49">
-        <v>226.6630000000001</v>
+        <v>237.0920000000001</v>
       </c>
       <c r="F49">
-        <v>490.1630000000001</v>
+        <v>500.5920000000001</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5433,37 +5433,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M49">
-        <v>115.5804354</v>
+        <v>118.0395936</v>
       </c>
       <c r="N49">
-        <v>-70.0471020666667</v>
+        <v>-72.5062602666667</v>
       </c>
       <c r="O49">
-        <v>-21.01413062000001</v>
+        <v>-21.75187808000001</v>
       </c>
       <c r="P49">
-        <v>-49.03297144666669</v>
+        <v>-50.75438218666669</v>
       </c>
       <c r="Q49">
-        <v>12.2670285533333</v>
+        <v>10.54561781333331</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1074746146978512</v>
+        <v>0.1086606649805022</v>
       </c>
       <c r="T49">
-        <v>1.424355997640905</v>
+        <v>1.451747459133999</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.1181860922458508</v>
+        <v>0.1157238819907289</v>
       </c>
       <c r="W49">
-        <v>0.2079317194484284</v>
+        <v>0.2085123086265861</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3939536408195026</v>
+        <v>0.3857462733024296</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1565894539306225</v>
+        <v>0.1584894539306225</v>
       </c>
       <c r="C50">
-        <v>-216.3530515016772</v>
+        <v>-231.5744609358315</v>
       </c>
       <c r="D50">
-        <v>284.2389484983228</v>
+        <v>279.4465390641685</v>
       </c>
       <c r="E50">
-        <v>237.092</v>
+        <v>247.521</v>
       </c>
       <c r="F50">
-        <v>500.592</v>
+        <v>511.021</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5515,37 +5515,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M50">
-        <v>118.0395936</v>
+        <v>120.4987518</v>
       </c>
       <c r="N50">
-        <v>-72.50626026666669</v>
+        <v>-74.96541846666668</v>
       </c>
       <c r="O50">
-        <v>-21.75187808</v>
+        <v>-22.48962554</v>
       </c>
       <c r="P50">
-        <v>-50.75438218666668</v>
+        <v>-52.47579292666667</v>
       </c>
       <c r="Q50">
-        <v>10.54561781333332</v>
+        <v>8.824207073333326</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1086606649805022</v>
+        <v>0.1098932270389434</v>
       </c>
       <c r="T50">
-        <v>1.451747459133999</v>
+        <v>1.480213095587607</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1157238819907289</v>
+        <v>0.1133621701133671</v>
       </c>
       <c r="W50">
-        <v>0.2085123086265861</v>
+        <v>0.209069200287268</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3857462733024296</v>
+        <v>0.3778739003778903</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1584894539306225</v>
+        <v>0.1603894539306225</v>
       </c>
       <c r="C51">
-        <v>-231.5744609358315</v>
+        <v>-246.6369451353756</v>
       </c>
       <c r="D51">
-        <v>279.4465390641685</v>
+        <v>274.8130548646244</v>
       </c>
       <c r="E51">
-        <v>247.521</v>
+        <v>257.95</v>
       </c>
       <c r="F51">
-        <v>511.021</v>
+        <v>521.45</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5597,37 +5597,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M51">
-        <v>120.4987518</v>
+        <v>122.95791</v>
       </c>
       <c r="N51">
-        <v>-74.96541846666668</v>
+        <v>-77.42457666666668</v>
       </c>
       <c r="O51">
-        <v>-22.48962554</v>
+        <v>-23.227373</v>
       </c>
       <c r="P51">
-        <v>-52.47579292666667</v>
+        <v>-54.19720366666668</v>
       </c>
       <c r="Q51">
-        <v>8.824207073333326</v>
+        <v>7.102796333333316</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1098932270389434</v>
+        <v>0.1111750915797223</v>
       </c>
       <c r="T51">
-        <v>1.480213095587607</v>
+        <v>1.509817357499359</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1133621701133671</v>
+        <v>0.1110949267110997</v>
       </c>
       <c r="W51">
-        <v>0.209069200287268</v>
+        <v>0.2096038162815227</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3778739003778903</v>
+        <v>0.3703164223703325</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1603894539306225</v>
+        <v>0.1622894539306225</v>
       </c>
       <c r="C52">
-        <v>-246.6369451353756</v>
+        <v>-261.5482805453583</v>
       </c>
       <c r="D52">
-        <v>274.8130548646244</v>
+        <v>270.3307194546417</v>
       </c>
       <c r="E52">
-        <v>257.95</v>
+        <v>268.379</v>
       </c>
       <c r="F52">
-        <v>521.45</v>
+        <v>531.879</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5679,37 +5679,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M52">
-        <v>122.95791</v>
+        <v>125.4170682</v>
       </c>
       <c r="N52">
-        <v>-77.42457666666668</v>
+        <v>-79.88373486666667</v>
       </c>
       <c r="O52">
-        <v>-23.227373</v>
+        <v>-23.96512046</v>
       </c>
       <c r="P52">
-        <v>-54.19720366666668</v>
+        <v>-55.91861440666667</v>
       </c>
       <c r="Q52">
-        <v>7.102796333333316</v>
+        <v>5.381385593333327</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1111750915797223</v>
+        <v>0.1125092771221656</v>
       </c>
       <c r="T52">
-        <v>1.509817357499359</v>
+        <v>1.540629956631999</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1110949267110997</v>
+        <v>0.1089165948148037</v>
       </c>
       <c r="W52">
-        <v>0.2096038162815227</v>
+        <v>0.2101174669426693</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3703164223703325</v>
+        <v>0.3630553160493456</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1622894539306225</v>
+        <v>0.1641894539306225</v>
       </c>
       <c r="C53">
-        <v>-261.5482805453583</v>
+        <v>-276.3157444026612</v>
       </c>
       <c r="D53">
-        <v>270.3307194546417</v>
+        <v>265.9922555973389</v>
       </c>
       <c r="E53">
-        <v>268.379</v>
+        <v>278.8080000000001</v>
       </c>
       <c r="F53">
-        <v>531.879</v>
+        <v>542.3080000000001</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5761,37 +5761,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M53">
-        <v>125.4170682</v>
+        <v>127.8762264</v>
       </c>
       <c r="N53">
-        <v>-79.88373486666667</v>
+        <v>-82.3428930666667</v>
       </c>
       <c r="O53">
-        <v>-23.96512046</v>
+        <v>-24.70286792000001</v>
       </c>
       <c r="P53">
-        <v>-55.91861440666667</v>
+        <v>-57.64002514666669</v>
       </c>
       <c r="Q53">
-        <v>5.381385593333327</v>
+        <v>3.659974853333303</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1125092771221656</v>
+        <v>0.1138990537288774</v>
       </c>
       <c r="T53">
-        <v>1.540629956631999</v>
+        <v>1.572726414061833</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1089165948148037</v>
+        <v>0.106822044914519</v>
       </c>
       <c r="W53">
-        <v>0.2101174669426693</v>
+        <v>0.2106113618091564</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3630553160493456</v>
+        <v>0.3560734830483966</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1641894539306225</v>
+        <v>0.1660894539306225</v>
       </c>
       <c r="C54">
-        <v>-276.3157444026612</v>
+        <v>-290.9461541615452</v>
       </c>
       <c r="D54">
-        <v>265.9922555973389</v>
+        <v>261.7908458384549</v>
       </c>
       <c r="E54">
-        <v>278.8080000000001</v>
+        <v>289.2370000000001</v>
       </c>
       <c r="F54">
-        <v>542.3080000000001</v>
+        <v>552.7370000000001</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5843,37 +5843,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M54">
-        <v>127.8762264</v>
+        <v>130.3353846</v>
       </c>
       <c r="N54">
-        <v>-82.3428930666667</v>
+        <v>-84.80205126666669</v>
       </c>
       <c r="O54">
-        <v>-24.70286792000001</v>
+        <v>-25.44061538000001</v>
       </c>
       <c r="P54">
-        <v>-57.64002514666669</v>
+        <v>-59.36143588666668</v>
       </c>
       <c r="Q54">
-        <v>3.659974853333303</v>
+        <v>1.938564113333314</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1138990537288774</v>
+        <v>0.115347969765662</v>
       </c>
       <c r="T54">
-        <v>1.572726414061833</v>
+        <v>1.606188678190808</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.106822044914519</v>
+        <v>0.1048065346331129</v>
       </c>
       <c r="W54">
-        <v>0.2106113618091564</v>
+        <v>0.211086619133512</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3560734830483966</v>
+        <v>0.3493551154437099</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1660894539306225</v>
+        <v>0.1679894539306225</v>
       </c>
       <c r="C55">
-        <v>-290.9461541615452</v>
+        <v>-305.4459032408845</v>
       </c>
       <c r="D55">
-        <v>261.7908458384549</v>
+        <v>257.7200967591156</v>
       </c>
       <c r="E55">
-        <v>289.2370000000001</v>
+        <v>299.6660000000001</v>
       </c>
       <c r="F55">
-        <v>552.7370000000001</v>
+        <v>563.1660000000001</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5925,37 +5925,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M55">
-        <v>130.3353846</v>
+        <v>132.7945428</v>
       </c>
       <c r="N55">
-        <v>-84.80205126666669</v>
+        <v>-87.26120946666668</v>
       </c>
       <c r="O55">
-        <v>-25.44061538000001</v>
+        <v>-26.17836284000001</v>
       </c>
       <c r="P55">
-        <v>-59.36143588666668</v>
+        <v>-61.08284662666668</v>
       </c>
       <c r="Q55">
-        <v>1.938564113333314</v>
+        <v>0.2171533733333177</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.115347969765662</v>
+        <v>0.116859882151872</v>
       </c>
       <c r="T55">
-        <v>1.606188678190808</v>
+        <v>1.641105823368869</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1048065346331129</v>
+        <v>0.1028656728806479</v>
       </c>
       <c r="W55">
-        <v>0.211086619133512</v>
+        <v>0.2115442743347432</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3493551154437099</v>
+        <v>0.3428855762688263</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1679894539306225</v>
+        <v>0.1698894539306225</v>
       </c>
       <c r="C56">
-        <v>-305.4459032408845</v>
+        <v>-319.8209934873296</v>
       </c>
       <c r="D56">
-        <v>257.7200967591156</v>
+        <v>253.7740065126705</v>
       </c>
       <c r="E56">
-        <v>299.6660000000001</v>
+        <v>310.0950000000001</v>
       </c>
       <c r="F56">
-        <v>563.1660000000001</v>
+        <v>573.5950000000001</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -6007,37 +6007,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M56">
-        <v>132.7945428</v>
+        <v>135.253701</v>
       </c>
       <c r="N56">
-        <v>-87.26120946666668</v>
+        <v>-89.7203676666667</v>
       </c>
       <c r="O56">
-        <v>-26.17836284000001</v>
+        <v>-26.91611030000001</v>
       </c>
       <c r="P56">
-        <v>-61.08284662666668</v>
+        <v>-62.80425736666669</v>
       </c>
       <c r="Q56">
-        <v>0.2171533733333177</v>
+        <v>-1.504257366666693</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.116859882151872</v>
+        <v>0.1184389906441358</v>
       </c>
       <c r="T56">
-        <v>1.641105823368869</v>
+        <v>1.677574841665955</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1028656728806479</v>
+        <v>0.1009953879191816</v>
       </c>
       <c r="W56">
-        <v>0.2115442743347432</v>
+        <v>0.211985287528657</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3428855762688263</v>
+        <v>0.3366512930639386</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1698894539306225</v>
+        <v>0.1717894539306225</v>
       </c>
       <c r="C57">
-        <v>-319.8209934873296</v>
+        <v>-334.0770647010804</v>
       </c>
       <c r="D57">
-        <v>253.7740065126705</v>
+        <v>249.9469352989197</v>
       </c>
       <c r="E57">
-        <v>310.0950000000001</v>
+        <v>320.5240000000001</v>
       </c>
       <c r="F57">
-        <v>573.5950000000001</v>
+        <v>584.0240000000001</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -6089,37 +6089,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M57">
-        <v>135.253701</v>
+        <v>137.7128592</v>
       </c>
       <c r="N57">
-        <v>-89.7203676666667</v>
+        <v>-92.17952586666669</v>
       </c>
       <c r="O57">
-        <v>-26.91611030000001</v>
+        <v>-27.65385776000001</v>
       </c>
       <c r="P57">
-        <v>-62.80425736666669</v>
+        <v>-64.52566810666669</v>
       </c>
       <c r="Q57">
-        <v>-1.504257366666693</v>
+        <v>-3.225668106666689</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1184389906441358</v>
+        <v>0.1200898767951389</v>
       </c>
       <c r="T57">
-        <v>1.677574841665955</v>
+        <v>1.715701542612909</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1009953879191816</v>
+        <v>0.0991918988491962</v>
       </c>
       <c r="W57">
-        <v>0.211985287528657</v>
+        <v>0.2124105502513595</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3366512930639386</v>
+        <v>0.3306396628306539</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1717894539306225</v>
+        <v>0.1736894539306225</v>
       </c>
       <c r="C58">
-        <v>-334.0770647010804</v>
+        <v>-348.2194215297488</v>
       </c>
       <c r="D58">
-        <v>249.9469352989197</v>
+        <v>246.2335784702513</v>
       </c>
       <c r="E58">
-        <v>320.5240000000001</v>
+        <v>330.9530000000001</v>
       </c>
       <c r="F58">
-        <v>584.0240000000001</v>
+        <v>594.4530000000001</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6171,37 +6171,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M58">
-        <v>137.7128592</v>
+        <v>140.1720174</v>
       </c>
       <c r="N58">
-        <v>-92.17952586666669</v>
+        <v>-94.63868406666668</v>
       </c>
       <c r="O58">
-        <v>-27.65385776000001</v>
+        <v>-28.39160522000001</v>
       </c>
       <c r="P58">
-        <v>-64.52566810666669</v>
+        <v>-66.24707884666668</v>
       </c>
       <c r="Q58">
-        <v>-3.225668106666689</v>
+        <v>-4.947078846666685</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1200898767951389</v>
+        <v>0.1218175483485143</v>
       </c>
       <c r="T58">
-        <v>1.715701542612909</v>
+        <v>1.755601578487627</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.0991918988491962</v>
+        <v>0.09745169009745591</v>
       </c>
       <c r="W58">
-        <v>0.2124105502513595</v>
+        <v>0.2128208914750199</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3306396628306539</v>
+        <v>0.3248389669915197</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1736894539306225</v>
+        <v>0.1755894539306225</v>
       </c>
       <c r="C59">
-        <v>-348.2194215297488</v>
+        <v>-362.2530580000091</v>
       </c>
       <c r="D59">
-        <v>246.2335784702513</v>
+        <v>242.6289419999911</v>
       </c>
       <c r="E59">
-        <v>330.9530000000001</v>
+        <v>341.3820000000002</v>
       </c>
       <c r="F59">
-        <v>594.4530000000001</v>
+        <v>604.8820000000002</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6253,37 +6253,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M59">
-        <v>140.1720174</v>
+        <v>142.6311756</v>
       </c>
       <c r="N59">
-        <v>-94.63868406666668</v>
+        <v>-97.0978422666667</v>
       </c>
       <c r="O59">
-        <v>-28.39160522000001</v>
+        <v>-29.12935268000001</v>
       </c>
       <c r="P59">
-        <v>-66.24707884666668</v>
+        <v>-67.96848958666669</v>
       </c>
       <c r="Q59">
-        <v>-4.947078846666685</v>
+        <v>-6.668489586666695</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1218175483485143</v>
+        <v>0.1236274899758598</v>
       </c>
       <c r="T59">
-        <v>1.755601578487627</v>
+        <v>1.797401616070666</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.09745169009745591</v>
+        <v>0.09577148854405147</v>
       </c>
       <c r="W59">
-        <v>0.2128208914750199</v>
+        <v>0.2132170830013127</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3248389669915197</v>
+        <v>0.3192382951468383</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1755894539306225</v>
+        <v>0.1774894539306225</v>
       </c>
       <c r="C60">
-        <v>-362.253058000009</v>
+        <v>-376.1826799256101</v>
       </c>
       <c r="D60">
-        <v>242.6289419999911</v>
+        <v>239.1283200743899</v>
       </c>
       <c r="E60">
-        <v>341.3820000000001</v>
+        <v>351.811</v>
       </c>
       <c r="F60">
-        <v>604.8820000000001</v>
+        <v>615.311</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6335,37 +6335,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M60">
-        <v>142.6311756</v>
+        <v>145.0903338</v>
       </c>
       <c r="N60">
-        <v>-97.0978422666667</v>
+        <v>-99.55700046666669</v>
       </c>
       <c r="O60">
-        <v>-29.12935268000001</v>
+        <v>-29.86710014000001</v>
       </c>
       <c r="P60">
-        <v>-67.96848958666669</v>
+        <v>-69.68990032666669</v>
       </c>
       <c r="Q60">
-        <v>-6.668489586666695</v>
+        <v>-8.389900326666691</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1236274899758598</v>
+        <v>0.1255257214386857</v>
       </c>
       <c r="T60">
-        <v>1.797401616070665</v>
+        <v>1.841240679877267</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.09577148854405147</v>
+        <v>0.09414824297550825</v>
       </c>
       <c r="W60">
-        <v>0.2132170830013127</v>
+        <v>0.2135998443063752</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3192382951468383</v>
+        <v>0.3138274765850275</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1774894539306225</v>
+        <v>0.1793894539306225</v>
       </c>
       <c r="C61">
-        <v>-376.1826799256101</v>
+        <v>-390.0127254031768</v>
       </c>
       <c r="D61">
-        <v>239.1283200743899</v>
+        <v>235.7272745968232</v>
       </c>
       <c r="E61">
-        <v>351.811</v>
+        <v>362.24</v>
       </c>
       <c r="F61">
-        <v>615.311</v>
+        <v>625.74</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6417,37 +6417,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M61">
-        <v>145.0903338</v>
+        <v>147.549492</v>
       </c>
       <c r="N61">
-        <v>-99.55700046666669</v>
+        <v>-102.0161586666667</v>
       </c>
       <c r="O61">
-        <v>-29.86710014000001</v>
+        <v>-30.6048476</v>
       </c>
       <c r="P61">
-        <v>-69.68990032666669</v>
+        <v>-71.41131106666668</v>
       </c>
       <c r="Q61">
-        <v>-8.389900326666691</v>
+        <v>-10.11131106666669</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1255257214386857</v>
+        <v>0.1275188644746528</v>
       </c>
       <c r="T61">
-        <v>1.841240679877267</v>
+        <v>1.887271696874199</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.09414824297550825</v>
+        <v>0.09257910559258312</v>
       </c>
       <c r="W61">
-        <v>0.2135998443063752</v>
+        <v>0.2139698469012689</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3138274765850275</v>
+        <v>0.3085970186419438</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1793894539306225</v>
+        <v>0.1812894539306225</v>
       </c>
       <c r="C62">
-        <v>-390.0127254031768</v>
+        <v>-403.747383583505</v>
       </c>
       <c r="D62">
-        <v>235.7272745968232</v>
+        <v>232.4216164164951</v>
       </c>
       <c r="E62">
-        <v>362.24</v>
+        <v>372.6690000000001</v>
       </c>
       <c r="F62">
-        <v>625.74</v>
+        <v>636.1690000000001</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6499,37 +6499,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M62">
-        <v>147.549492</v>
+        <v>150.0086502</v>
       </c>
       <c r="N62">
-        <v>-102.0161586666667</v>
+        <v>-104.4753168666667</v>
       </c>
       <c r="O62">
-        <v>-30.6048476</v>
+        <v>-31.34259506000001</v>
       </c>
       <c r="P62">
-        <v>-71.41131106666668</v>
+        <v>-73.13272180666669</v>
       </c>
       <c r="Q62">
-        <v>-10.11131106666669</v>
+        <v>-11.8327218066667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1275188644746528</v>
+        <v>0.1296142199740029</v>
       </c>
       <c r="T62">
-        <v>1.887271696874199</v>
+        <v>1.935663278845333</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.09257910559258312</v>
+        <v>0.09106141533696699</v>
       </c>
       <c r="W62">
-        <v>0.2139698469012689</v>
+        <v>0.2143277182635432</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3085970186419438</v>
+        <v>0.3035380511232233</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1812894539306225</v>
+        <v>0.1831894539306225</v>
       </c>
       <c r="C63">
-        <v>-403.747383583505</v>
+        <v>-417.3906118852955</v>
       </c>
       <c r="D63">
-        <v>232.4216164164951</v>
+        <v>229.2073881147045</v>
       </c>
       <c r="E63">
-        <v>372.6690000000001</v>
+        <v>383.0980000000001</v>
       </c>
       <c r="F63">
-        <v>636.1690000000001</v>
+        <v>646.5980000000001</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6581,37 +6581,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M63">
-        <v>150.0086502</v>
+        <v>152.4678084</v>
       </c>
       <c r="N63">
-        <v>-104.4753168666667</v>
+        <v>-106.9344750666667</v>
       </c>
       <c r="O63">
-        <v>-31.34259506000001</v>
+        <v>-32.08034252000001</v>
       </c>
       <c r="P63">
-        <v>-73.13272180666669</v>
+        <v>-74.85413254666668</v>
       </c>
       <c r="Q63">
-        <v>-11.8327218066667</v>
+        <v>-13.55413254666668</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1296142199740029</v>
+        <v>0.1318198573417398</v>
       </c>
       <c r="T63">
-        <v>1.935663278845333</v>
+        <v>1.986601786183368</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.09106141533696699</v>
+        <v>0.08959268283153203</v>
       </c>
       <c r="W63">
-        <v>0.2143277182635432</v>
+        <v>0.2146740453883248</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3035380511232233</v>
+        <v>0.2986422761051069</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1831894539306225</v>
+        <v>0.1850894539306225</v>
       </c>
       <c r="C64">
-        <v>-417.3906118852955</v>
+        <v>-430.9461518000463</v>
       </c>
       <c r="D64">
-        <v>229.2073881147045</v>
+        <v>226.0808481999537</v>
       </c>
       <c r="E64">
-        <v>383.0980000000001</v>
+        <v>393.527</v>
       </c>
       <c r="F64">
-        <v>646.5980000000001</v>
+        <v>657.027</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6663,37 +6663,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M64">
-        <v>152.4678084</v>
+        <v>154.9269666</v>
       </c>
       <c r="N64">
-        <v>-106.9344750666667</v>
+        <v>-109.3936332666667</v>
       </c>
       <c r="O64">
-        <v>-32.08034252000001</v>
+        <v>-32.81808998</v>
       </c>
       <c r="P64">
-        <v>-74.85413254666668</v>
+        <v>-76.57554328666669</v>
       </c>
       <c r="Q64">
-        <v>-13.55413254666668</v>
+        <v>-15.27554328666669</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1318198573417398</v>
+        <v>0.134144718350976</v>
       </c>
       <c r="T64">
-        <v>1.986601786183368</v>
+        <v>2.040293726350486</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08959268283153203</v>
+        <v>0.08817057675484107</v>
       </c>
       <c r="W64">
-        <v>0.2146740453883248</v>
+        <v>0.2150093780012085</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2986422761051069</v>
+        <v>0.2939019225161369</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1850894539306225</v>
+        <v>0.1869894539306225</v>
       </c>
       <c r="C65">
-        <v>-430.9461518000463</v>
+        <v>-444.4175434208183</v>
       </c>
       <c r="D65">
-        <v>226.0808481999537</v>
+        <v>223.0384565791817</v>
       </c>
       <c r="E65">
-        <v>393.527</v>
+        <v>403.956</v>
       </c>
       <c r="F65">
-        <v>657.027</v>
+        <v>667.456</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6745,37 +6745,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M65">
-        <v>154.9269666</v>
+        <v>157.3861248</v>
       </c>
       <c r="N65">
-        <v>-109.3936332666667</v>
+        <v>-111.8527914666667</v>
       </c>
       <c r="O65">
-        <v>-32.81808998</v>
+        <v>-33.55583744</v>
       </c>
       <c r="P65">
-        <v>-76.57554328666669</v>
+        <v>-78.29695402666667</v>
       </c>
       <c r="Q65">
-        <v>-15.27554328666669</v>
+        <v>-16.99695402666667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.134144718350976</v>
+        <v>0.1365987383051698</v>
       </c>
       <c r="T65">
-        <v>2.040293726350486</v>
+        <v>2.096968552082443</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08817057675484107</v>
+        <v>0.08679291149304669</v>
       </c>
       <c r="W65">
-        <v>0.2150093780012085</v>
+        <v>0.2153342314699396</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2939019225161369</v>
+        <v>0.2893097049768223</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1869894539306225</v>
+        <v>0.1888894539306225</v>
       </c>
       <c r="C66">
-        <v>-444.4175434208183</v>
+        <v>-457.8081388134874</v>
       </c>
       <c r="D66">
-        <v>223.0384565791817</v>
+        <v>220.0768611865127</v>
       </c>
       <c r="E66">
-        <v>403.956</v>
+        <v>414.3850000000001</v>
       </c>
       <c r="F66">
-        <v>667.456</v>
+        <v>677.8850000000001</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6827,37 +6827,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M66">
-        <v>157.3861248</v>
+        <v>159.845283</v>
       </c>
       <c r="N66">
-        <v>-111.8527914666667</v>
+        <v>-114.3119496666667</v>
       </c>
       <c r="O66">
-        <v>-33.55583744</v>
+        <v>-34.29358490000001</v>
       </c>
       <c r="P66">
-        <v>-78.29695402666667</v>
+        <v>-80.01836476666668</v>
       </c>
       <c r="Q66">
-        <v>-16.99695402666667</v>
+        <v>-18.71836476666668</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1365987383051698</v>
+        <v>0.1391929879710318</v>
       </c>
       <c r="T66">
-        <v>2.096968552082443</v>
+        <v>2.156881939284799</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.08679291149304669</v>
+        <v>0.08545763593161518</v>
       </c>
       <c r="W66">
-        <v>0.2153342314699396</v>
+        <v>0.2156490894473252</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2893097049768223</v>
+        <v>0.2848587864387173</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1888894539306225</v>
+        <v>0.1907894539306225</v>
       </c>
       <c r="C67">
-        <v>-457.8081388134874</v>
+        <v>-471.1211143366621</v>
       </c>
       <c r="D67">
-        <v>220.0768611865127</v>
+        <v>217.192885663338</v>
       </c>
       <c r="E67">
-        <v>414.3850000000001</v>
+        <v>424.8140000000001</v>
       </c>
       <c r="F67">
-        <v>677.8850000000001</v>
+        <v>688.3140000000001</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6909,37 +6909,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M67">
-        <v>159.845283</v>
+        <v>162.3044412</v>
       </c>
       <c r="N67">
-        <v>-114.3119496666667</v>
+        <v>-116.7711078666667</v>
       </c>
       <c r="O67">
-        <v>-34.29358490000001</v>
+        <v>-35.03133236</v>
       </c>
       <c r="P67">
-        <v>-80.01836476666668</v>
+        <v>-81.73977550666669</v>
       </c>
       <c r="Q67">
-        <v>-18.71836476666668</v>
+        <v>-20.43977550666669</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1391929879710318</v>
+        <v>0.1419398405584151</v>
       </c>
       <c r="T67">
-        <v>2.156881939284799</v>
+        <v>2.220319643381411</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.08545763593161518</v>
+        <v>0.08416282326598465</v>
       </c>
       <c r="W67">
-        <v>0.2156490894473252</v>
+        <v>0.2159544062738808</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2848587864387173</v>
+        <v>0.2805427442199488</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1907894539306225</v>
+        <v>0.1926894539306225</v>
       </c>
       <c r="C68">
-        <v>-471.1211143366621</v>
+        <v>-484.3594820054617</v>
       </c>
       <c r="D68">
-        <v>217.192885663338</v>
+        <v>214.3835179945384</v>
       </c>
       <c r="E68">
-        <v>424.8140000000001</v>
+        <v>435.2430000000001</v>
       </c>
       <c r="F68">
-        <v>688.3140000000001</v>
+        <v>698.7430000000001</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6991,37 +6991,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M68">
-        <v>162.3044412</v>
+        <v>164.7635994</v>
       </c>
       <c r="N68">
-        <v>-116.7711078666667</v>
+        <v>-119.2302660666667</v>
       </c>
       <c r="O68">
-        <v>-35.03133236</v>
+        <v>-35.76907982000001</v>
       </c>
       <c r="P68">
-        <v>-81.73977550666669</v>
+        <v>-83.4611862466667</v>
       </c>
       <c r="Q68">
-        <v>-20.43977550666669</v>
+        <v>-22.1611862466667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1419398405584151</v>
+        <v>0.1448531690601853</v>
       </c>
       <c r="T68">
-        <v>2.220319643381411</v>
+        <v>2.287602056817212</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08416282326598465</v>
+        <v>0.08290666172470128</v>
       </c>
       <c r="W68">
-        <v>0.2159544062738808</v>
+        <v>0.2162506091653154</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2805427442199488</v>
+        <v>0.2763555390823377</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1926894539306225</v>
+        <v>0.1945894539306225</v>
       </c>
       <c r="C69">
-        <v>-484.3594820054617</v>
+        <v>-497.5260999846202</v>
       </c>
       <c r="D69">
-        <v>214.3835179945384</v>
+        <v>211.6459000153799</v>
       </c>
       <c r="E69">
-        <v>435.2430000000001</v>
+        <v>445.6720000000001</v>
       </c>
       <c r="F69">
-        <v>698.7430000000001</v>
+        <v>709.1720000000001</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -7073,37 +7073,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M69">
-        <v>164.7635994</v>
+        <v>167.2227576000001</v>
       </c>
       <c r="N69">
-        <v>-119.2302660666667</v>
+        <v>-121.6894242666667</v>
       </c>
       <c r="O69">
-        <v>-35.76907982000001</v>
+        <v>-36.50682728000002</v>
       </c>
       <c r="P69">
-        <v>-83.4611862466667</v>
+        <v>-85.18259698666671</v>
       </c>
       <c r="Q69">
-        <v>-22.1611862466667</v>
+        <v>-23.88259698666671</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1448531690601853</v>
+        <v>0.1479485805933161</v>
       </c>
       <c r="T69">
-        <v>2.287602056817212</v>
+        <v>2.359089621092749</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08290666172470128</v>
+        <v>0.08168744611110274</v>
       </c>
       <c r="W69">
-        <v>0.2162506091653154</v>
+        <v>0.216538100207002</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2763555390823377</v>
+        <v>0.2722914870370091</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1945894539306225</v>
+        <v>0.1964894539306225</v>
       </c>
       <c r="C70">
-        <v>-497.5260999846202</v>
+        <v>-510.6236822877611</v>
       </c>
       <c r="D70">
-        <v>211.6459000153799</v>
+        <v>208.977317712239</v>
       </c>
       <c r="E70">
-        <v>445.6720000000001</v>
+        <v>456.1010000000001</v>
       </c>
       <c r="F70">
-        <v>709.1720000000001</v>
+        <v>719.6010000000001</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7155,37 +7155,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M70">
-        <v>167.2227576000001</v>
+        <v>169.6819158</v>
       </c>
       <c r="N70">
-        <v>-121.6894242666667</v>
+        <v>-124.1485824666667</v>
       </c>
       <c r="O70">
-        <v>-36.50682728000002</v>
+        <v>-37.24457474000001</v>
       </c>
       <c r="P70">
-        <v>-85.18259698666671</v>
+        <v>-86.90400772666669</v>
       </c>
       <c r="Q70">
-        <v>-23.88259698666671</v>
+        <v>-25.60400772666669</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1479485805933161</v>
+        <v>0.1512436960963263</v>
       </c>
       <c r="T70">
-        <v>2.359089621092749</v>
+        <v>2.43518928628929</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08168744611110274</v>
+        <v>0.08050357008050704</v>
       </c>
       <c r="W70">
-        <v>0.216538100207002</v>
+        <v>0.2168172581750165</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2722914870370091</v>
+        <v>0.2683452336016902</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1964894539306225</v>
+        <v>0.1983894539306225</v>
       </c>
       <c r="C71">
-        <v>-510.6236822877611</v>
+        <v>-523.6548077520397</v>
       </c>
       <c r="D71">
-        <v>208.977317712239</v>
+        <v>206.3751922479604</v>
       </c>
       <c r="E71">
-        <v>456.1010000000001</v>
+        <v>466.5300000000001</v>
       </c>
       <c r="F71">
-        <v>719.6010000000001</v>
+        <v>730.0300000000001</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7237,37 +7237,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M71">
-        <v>169.6819158</v>
+        <v>172.141074</v>
       </c>
       <c r="N71">
-        <v>-124.1485824666667</v>
+        <v>-126.6077406666667</v>
       </c>
       <c r="O71">
-        <v>-37.24457474000001</v>
+        <v>-37.98232220000001</v>
       </c>
       <c r="P71">
-        <v>-86.90400772666669</v>
+        <v>-88.6254184666667</v>
       </c>
       <c r="Q71">
-        <v>-25.60400772666669</v>
+        <v>-27.3254184666667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1512436960963263</v>
+        <v>0.1547584859662038</v>
       </c>
       <c r="T71">
-        <v>2.43518928628929</v>
+        <v>2.516362262498933</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08050357008050704</v>
+        <v>0.07935351907935695</v>
       </c>
       <c r="W71">
-        <v>0.2168172581750165</v>
+        <v>0.2170884402010876</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2683452336016902</v>
+        <v>0.2645117302645231</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1983894539306225</v>
+        <v>0.2002894539306225</v>
       </c>
       <c r="C72">
-        <v>-523.6548077520397</v>
+        <v>-536.621928350532</v>
       </c>
       <c r="D72">
-        <v>206.3751922479604</v>
+        <v>203.8370716494681</v>
       </c>
       <c r="E72">
-        <v>466.5300000000001</v>
+        <v>476.9590000000002</v>
       </c>
       <c r="F72">
-        <v>730.0300000000001</v>
+        <v>740.4590000000002</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7319,37 +7319,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M72">
-        <v>172.141074</v>
+        <v>174.6002322000001</v>
       </c>
       <c r="N72">
-        <v>-126.6077406666667</v>
+        <v>-129.0668988666667</v>
       </c>
       <c r="O72">
-        <v>-37.98232220000001</v>
+        <v>-38.72006966000001</v>
       </c>
       <c r="P72">
-        <v>-88.6254184666667</v>
+        <v>-90.34682920666671</v>
       </c>
       <c r="Q72">
-        <v>-27.3254184666667</v>
+        <v>-29.04682920666671</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1547584859662038</v>
+        <v>0.1585156751374522</v>
       </c>
       <c r="T72">
-        <v>2.516362262498933</v>
+        <v>2.603133374998896</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07935351907935695</v>
+        <v>0.07823586388105613</v>
       </c>
       <c r="W72">
-        <v>0.2170884402010876</v>
+        <v>0.217351983296847</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2645117302645231</v>
+        <v>0.2607862129368538</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2002894539306225</v>
+        <v>0.2021894539306225</v>
       </c>
       <c r="C73">
-        <v>-536.6219283505318</v>
+        <v>-549.5273768986916</v>
       </c>
       <c r="D73">
-        <v>203.8370716494682</v>
+        <v>201.3606231013084</v>
       </c>
       <c r="E73">
-        <v>476.9590000000001</v>
+        <v>487.388</v>
       </c>
       <c r="F73">
-        <v>740.4590000000001</v>
+        <v>750.888</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7401,37 +7401,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M73">
-        <v>174.6002322</v>
+        <v>177.0593904</v>
       </c>
       <c r="N73">
-        <v>-129.0668988666667</v>
+        <v>-131.5260570666667</v>
       </c>
       <c r="O73">
-        <v>-38.72006966000001</v>
+        <v>-39.45781712</v>
       </c>
       <c r="P73">
-        <v>-90.34682920666668</v>
+        <v>-92.06823994666668</v>
       </c>
       <c r="Q73">
-        <v>-29.04682920666669</v>
+        <v>-30.76823994666668</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1585156751374522</v>
+        <v>0.1625412349637897</v>
       </c>
       <c r="T73">
-        <v>2.603133374998895</v>
+        <v>2.696102424105999</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07823586388105615</v>
+        <v>0.07714925466048593</v>
       </c>
       <c r="W73">
-        <v>0.217351983296847</v>
+        <v>0.2176082057510574</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2607862129368539</v>
+        <v>0.2571641822016197</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2021894539306225</v>
+        <v>0.2040894539306225</v>
       </c>
       <c r="C74">
-        <v>-549.5273768986916</v>
+        <v>-562.3733742057906</v>
       </c>
       <c r="D74">
-        <v>201.3606231013084</v>
+        <v>198.9436257942094</v>
       </c>
       <c r="E74">
-        <v>487.388</v>
+        <v>497.817</v>
       </c>
       <c r="F74">
-        <v>750.888</v>
+        <v>761.317</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7483,37 +7483,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M74">
-        <v>177.0593904</v>
+        <v>179.5185486</v>
       </c>
       <c r="N74">
-        <v>-131.5260570666667</v>
+        <v>-133.9852152666667</v>
       </c>
       <c r="O74">
-        <v>-39.45781712</v>
+        <v>-40.19556458</v>
       </c>
       <c r="P74">
-        <v>-92.06823994666668</v>
+        <v>-93.78965068666668</v>
       </c>
       <c r="Q74">
-        <v>-30.76823994666668</v>
+        <v>-32.48965068666668</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1625412349637897</v>
+        <v>0.1668649844068931</v>
       </c>
       <c r="T74">
-        <v>2.696102424105999</v>
+        <v>2.795958069443258</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07714925466048593</v>
+        <v>0.07609241555554778</v>
       </c>
       <c r="W74">
-        <v>0.2176082057510574</v>
+        <v>0.2178574084120019</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2571641822016197</v>
+        <v>0.2536413851851592</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2040894539306225</v>
+        <v>0.2059894539306225</v>
       </c>
       <c r="C75">
-        <v>-562.3733742057906</v>
+        <v>-575.1620357174199</v>
       </c>
       <c r="D75">
-        <v>198.9436257942094</v>
+        <v>196.5839642825802</v>
       </c>
       <c r="E75">
-        <v>497.817</v>
+        <v>508.2460000000001</v>
       </c>
       <c r="F75">
-        <v>761.317</v>
+        <v>771.7460000000001</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7565,37 +7565,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M75">
-        <v>179.5185486</v>
+        <v>181.9777068</v>
       </c>
       <c r="N75">
-        <v>-133.9852152666667</v>
+        <v>-136.4443734666667</v>
       </c>
       <c r="O75">
-        <v>-40.19556458</v>
+        <v>-40.93331204</v>
       </c>
       <c r="P75">
-        <v>-93.78965068666668</v>
+        <v>-95.51106142666669</v>
       </c>
       <c r="Q75">
-        <v>-32.48965068666668</v>
+        <v>-34.21106142666669</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1668649844068931</v>
+        <v>0.1715213299610044</v>
       </c>
       <c r="T75">
-        <v>2.795958069443258</v>
+        <v>2.903494918267998</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07609241555554778</v>
+        <v>0.07506413966966198</v>
       </c>
       <c r="W75">
-        <v>0.2178574084120019</v>
+        <v>0.2180998758658937</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2536413851851592</v>
+        <v>0.2502137988988733</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2059894539306225</v>
+        <v>0.2078894539306225</v>
       </c>
       <c r="C76">
-        <v>-575.1620357174199</v>
+        <v>-587.8953776908143</v>
       </c>
       <c r="D76">
-        <v>196.5839642825802</v>
+        <v>194.2796223091859</v>
       </c>
       <c r="E76">
-        <v>508.2460000000001</v>
+        <v>518.6750000000001</v>
       </c>
       <c r="F76">
-        <v>771.7460000000001</v>
+        <v>782.1750000000001</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7647,37 +7647,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M76">
-        <v>181.9777068</v>
+        <v>184.436865</v>
       </c>
       <c r="N76">
-        <v>-136.4443734666667</v>
+        <v>-138.9035316666667</v>
       </c>
       <c r="O76">
-        <v>-40.93331204</v>
+        <v>-41.67105950000001</v>
       </c>
       <c r="P76">
-        <v>-95.51106142666669</v>
+        <v>-97.23247216666667</v>
       </c>
       <c r="Q76">
-        <v>-34.21106142666669</v>
+        <v>-35.93247216666667</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1715213299610044</v>
+        <v>0.1765501831594445</v>
       </c>
       <c r="T76">
-        <v>2.903494918267998</v>
+        <v>3.019634714998718</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07506413966966198</v>
+        <v>0.0740632844740665</v>
       </c>
       <c r="W76">
-        <v>0.2180998758658937</v>
+        <v>0.2183358775210151</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2502137988988733</v>
+        <v>0.246877614913555</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2078894539306225</v>
+        <v>0.2097894539306225</v>
       </c>
       <c r="C77">
-        <v>-587.8953776908143</v>
+        <v>-600.5753229408888</v>
       </c>
       <c r="D77">
-        <v>194.2796223091859</v>
+        <v>192.0286770591113</v>
       </c>
       <c r="E77">
-        <v>518.6750000000001</v>
+        <v>529.104</v>
       </c>
       <c r="F77">
-        <v>782.1750000000001</v>
+        <v>792.604</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7729,37 +7729,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M77">
-        <v>184.436865</v>
+        <v>186.8960232</v>
       </c>
       <c r="N77">
-        <v>-138.9035316666667</v>
+        <v>-141.3626898666667</v>
       </c>
       <c r="O77">
-        <v>-41.67105950000001</v>
+        <v>-42.40880696000001</v>
       </c>
       <c r="P77">
-        <v>-97.23247216666667</v>
+        <v>-98.95388290666669</v>
       </c>
       <c r="Q77">
-        <v>-35.93247216666667</v>
+        <v>-37.65388290666669</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1765501831594445</v>
+        <v>0.1819981074577547</v>
       </c>
       <c r="T77">
-        <v>3.019634714998718</v>
+        <v>3.145452828123665</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0740632844740665</v>
+        <v>0.07308876757309193</v>
       </c>
       <c r="W77">
-        <v>0.2183358775210151</v>
+        <v>0.2185656686062649</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.246877614913555</v>
+        <v>0.2436292252436397</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2097894539306225</v>
+        <v>0.2116894539306225</v>
       </c>
       <c r="C78">
-        <v>-600.5753229408888</v>
+        <v>-613.2037061914052</v>
       </c>
       <c r="D78">
-        <v>192.0286770591113</v>
+        <v>189.8292938085949</v>
       </c>
       <c r="E78">
-        <v>529.104</v>
+        <v>539.5330000000001</v>
       </c>
       <c r="F78">
-        <v>792.604</v>
+        <v>803.0330000000001</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7811,37 +7811,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M78">
-        <v>186.8960232</v>
+        <v>189.3551814</v>
       </c>
       <c r="N78">
-        <v>-141.3626898666667</v>
+        <v>-143.8218480666667</v>
       </c>
       <c r="O78">
-        <v>-42.40880696000001</v>
+        <v>-43.14655442000002</v>
       </c>
       <c r="P78">
-        <v>-98.95388290666669</v>
+        <v>-100.6752936466667</v>
       </c>
       <c r="Q78">
-        <v>-37.65388290666669</v>
+        <v>-39.37529364666671</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1819981074577547</v>
+        <v>0.1879197643037441</v>
       </c>
       <c r="T78">
-        <v>3.145452828123665</v>
+        <v>3.282211646737738</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07308876757309193</v>
+        <v>0.0721395627994154</v>
       </c>
       <c r="W78">
-        <v>0.2185656686062649</v>
+        <v>0.2187894910918979</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2436292252436397</v>
+        <v>0.2404652093313847</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2116894539306225</v>
+        <v>0.2135894539306225</v>
       </c>
       <c r="C79">
-        <v>-613.2037061914052</v>
+        <v>-625.7822790625671</v>
       </c>
       <c r="D79">
-        <v>189.8292938085949</v>
+        <v>187.679720937433</v>
       </c>
       <c r="E79">
-        <v>539.5330000000001</v>
+        <v>549.9620000000001</v>
       </c>
       <c r="F79">
-        <v>803.0330000000001</v>
+        <v>813.4620000000001</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7893,37 +7893,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M79">
-        <v>189.3551814</v>
+        <v>191.8143396</v>
       </c>
       <c r="N79">
-        <v>-143.8218480666667</v>
+        <v>-146.2810062666667</v>
       </c>
       <c r="O79">
-        <v>-43.14655442000002</v>
+        <v>-43.88430188000001</v>
       </c>
       <c r="P79">
-        <v>-100.6752936466667</v>
+        <v>-102.3967043866667</v>
       </c>
       <c r="Q79">
-        <v>-39.37529364666671</v>
+        <v>-41.0967043866667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1879197643037441</v>
+        <v>0.1943797535902779</v>
       </c>
       <c r="T79">
-        <v>3.282211646737738</v>
+        <v>3.431403085225817</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0721395627994154</v>
+        <v>0.07121469660967931</v>
       </c>
       <c r="W79">
-        <v>0.2187894910918979</v>
+        <v>0.2190075745394376</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2404652093313847</v>
+        <v>0.2373823220322644</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2135894539306225</v>
+        <v>0.2154894539306225</v>
       </c>
       <c r="C80">
-        <v>-625.7822790625671</v>
+        <v>-638.3127147235416</v>
       </c>
       <c r="D80">
-        <v>187.679720937433</v>
+        <v>185.5782852764585</v>
       </c>
       <c r="E80">
-        <v>549.9620000000001</v>
+        <v>560.3910000000001</v>
       </c>
       <c r="F80">
-        <v>813.4620000000001</v>
+        <v>823.8910000000001</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7975,37 +7975,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M80">
-        <v>191.8143396</v>
+        <v>194.2734978</v>
       </c>
       <c r="N80">
-        <v>-146.2810062666667</v>
+        <v>-148.7401644666667</v>
       </c>
       <c r="O80">
-        <v>-43.88430188000001</v>
+        <v>-44.62204934000001</v>
       </c>
       <c r="P80">
-        <v>-102.3967043866667</v>
+        <v>-104.1181151266667</v>
       </c>
       <c r="Q80">
-        <v>-41.0967043866667</v>
+        <v>-42.81811512666668</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1943797535902779</v>
+        <v>0.2014549799517197</v>
       </c>
       <c r="T80">
-        <v>3.431403085225817</v>
+        <v>3.594803232141332</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07121469660967931</v>
+        <v>0.07031324475386058</v>
       </c>
       <c r="W80">
-        <v>0.2190075745394376</v>
+        <v>0.2192201368870397</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2373823220322644</v>
+        <v>0.2343774825128686</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2154894539306225</v>
+        <v>0.2173894539306225</v>
       </c>
       <c r="C81">
-        <v>-638.3127147235416</v>
+        <v>-650.7966122358786</v>
       </c>
       <c r="D81">
-        <v>185.5782852764585</v>
+        <v>183.5233877641216</v>
       </c>
       <c r="E81">
-        <v>560.3910000000001</v>
+        <v>570.8200000000002</v>
       </c>
       <c r="F81">
-        <v>823.8910000000001</v>
+        <v>834.3200000000002</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -8057,37 +8057,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M81">
-        <v>194.2734978</v>
+        <v>196.732656</v>
       </c>
       <c r="N81">
-        <v>-148.7401644666667</v>
+        <v>-151.1993226666667</v>
       </c>
       <c r="O81">
-        <v>-44.62204934000001</v>
+        <v>-45.35979680000001</v>
       </c>
       <c r="P81">
-        <v>-104.1181151266667</v>
+        <v>-105.8395258666667</v>
       </c>
       <c r="Q81">
-        <v>-42.81811512666668</v>
+        <v>-44.53952586666671</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2014549799517197</v>
+        <v>0.2092377289493057</v>
       </c>
       <c r="T81">
-        <v>3.594803232141332</v>
+        <v>3.774543393748399</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07031324475386058</v>
+        <v>0.06943432919443732</v>
       </c>
       <c r="W81">
-        <v>0.2192201368870397</v>
+        <v>0.2194273851759517</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2343774825128686</v>
+        <v>0.2314477639814577</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2173894539306225</v>
+        <v>0.2192894539306225</v>
       </c>
       <c r="C82">
-        <v>-650.7966122358786</v>
+        <v>-663.2355006115216</v>
       </c>
       <c r="D82">
-        <v>183.5233877641216</v>
+        <v>181.5134993884785</v>
       </c>
       <c r="E82">
-        <v>570.8200000000002</v>
+        <v>581.2490000000001</v>
       </c>
       <c r="F82">
-        <v>834.3200000000002</v>
+        <v>844.7490000000001</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -8139,37 +8139,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M82">
-        <v>196.732656</v>
+        <v>199.1918142</v>
       </c>
       <c r="N82">
-        <v>-151.1993226666667</v>
+        <v>-153.6584808666667</v>
       </c>
       <c r="O82">
-        <v>-45.35979680000001</v>
+        <v>-46.09754426000001</v>
       </c>
       <c r="P82">
-        <v>-105.8395258666667</v>
+        <v>-107.5609366066667</v>
       </c>
       <c r="Q82">
-        <v>-44.53952586666671</v>
+        <v>-46.2609366066667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2092377289493057</v>
+        <v>0.2178397146834797</v>
       </c>
       <c r="T82">
-        <v>3.774543393748399</v>
+        <v>3.973203572366736</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06943432919443732</v>
+        <v>0.06857711525376527</v>
       </c>
       <c r="W82">
-        <v>0.2194273851759517</v>
+        <v>0.2196295162231622</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2314477639814577</v>
+        <v>0.2285903841792175</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2192894539306225</v>
+        <v>0.2211894539306225</v>
       </c>
       <c r="C83">
-        <v>-663.2355006115216</v>
+        <v>-675.6308426070588</v>
       </c>
       <c r="D83">
-        <v>181.5134993884785</v>
+        <v>179.5471573929413</v>
       </c>
       <c r="E83">
-        <v>581.2490000000001</v>
+        <v>591.6780000000001</v>
       </c>
       <c r="F83">
-        <v>844.7490000000001</v>
+        <v>855.1780000000001</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8221,37 +8221,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M83">
-        <v>199.1918142</v>
+        <v>201.6509724</v>
       </c>
       <c r="N83">
-        <v>-153.6584808666667</v>
+        <v>-156.1176390666667</v>
       </c>
       <c r="O83">
-        <v>-46.09754426000001</v>
+        <v>-46.83529172000001</v>
       </c>
       <c r="P83">
-        <v>-107.5609366066667</v>
+        <v>-109.2823473466667</v>
       </c>
       <c r="Q83">
-        <v>-46.2609366066667</v>
+        <v>-47.98234734666669</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2178397146834797</v>
+        <v>0.2273974766103397</v>
       </c>
       <c r="T83">
-        <v>3.973203572366736</v>
+        <v>4.193937104164888</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06857711525376527</v>
+        <v>0.06774080897018277</v>
       </c>
       <c r="W83">
-        <v>0.2196295162231622</v>
+        <v>0.2198267172448309</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2285903841792175</v>
+        <v>0.2258026965672759</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2211894539306225</v>
+        <v>0.2230894539306225</v>
       </c>
       <c r="C84">
-        <v>-675.6308426070588</v>
+        <v>-687.984038273994</v>
       </c>
       <c r="D84">
-        <v>179.5471573929413</v>
+        <v>177.6229617260063</v>
       </c>
       <c r="E84">
-        <v>591.6780000000001</v>
+        <v>602.1070000000002</v>
       </c>
       <c r="F84">
-        <v>855.1780000000001</v>
+        <v>865.6070000000002</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8303,37 +8303,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M84">
-        <v>201.6509724</v>
+        <v>204.1101306</v>
       </c>
       <c r="N84">
-        <v>-156.1176390666667</v>
+        <v>-158.5767972666667</v>
       </c>
       <c r="O84">
-        <v>-46.83529172000001</v>
+        <v>-47.57303918000002</v>
       </c>
       <c r="P84">
-        <v>-109.2823473466667</v>
+        <v>-111.0037580866667</v>
       </c>
       <c r="Q84">
-        <v>-47.98234734666669</v>
+        <v>-49.7037580866667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2273974766103397</v>
+        <v>0.2380796811168303</v>
       </c>
       <c r="T84">
-        <v>4.193937104164888</v>
+        <v>4.440639286762823</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06774080897018277</v>
+        <v>0.06692465464524079</v>
       </c>
       <c r="W84">
-        <v>0.2198267172448309</v>
+        <v>0.2200191664346522</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2258026965672759</v>
+        <v>0.2230821821508027</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2230894539306225</v>
+        <v>0.2249894539306225</v>
       </c>
       <c r="C85">
-        <v>-687.984038273994</v>
+        <v>-700.296428283152</v>
       </c>
       <c r="D85">
-        <v>177.6229617260063</v>
+        <v>175.7395717168482</v>
       </c>
       <c r="E85">
-        <v>602.1070000000002</v>
+        <v>612.5360000000002</v>
       </c>
       <c r="F85">
-        <v>865.6070000000002</v>
+        <v>876.0360000000002</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8385,37 +8385,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M85">
-        <v>204.1101306</v>
+        <v>206.5692888</v>
       </c>
       <c r="N85">
-        <v>-158.5767972666667</v>
+        <v>-161.0359554666667</v>
       </c>
       <c r="O85">
-        <v>-47.57303918000002</v>
+        <v>-48.31078664000001</v>
       </c>
       <c r="P85">
-        <v>-111.0037580866667</v>
+        <v>-112.7251688266667</v>
       </c>
       <c r="Q85">
-        <v>-49.7037580866667</v>
+        <v>-51.42516882666671</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2380796811168303</v>
+        <v>0.2500971611866322</v>
       </c>
       <c r="T85">
-        <v>4.440639286762823</v>
+        <v>4.7181792421855</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06692465464524079</v>
+        <v>0.0661279325661308</v>
       </c>
       <c r="W85">
-        <v>0.2200191664346522</v>
+        <v>0.2202070335009064</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2230821821508027</v>
+        <v>0.2204264418871027</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2249894539306225</v>
+        <v>0.2268894539306225</v>
       </c>
       <c r="C86">
-        <v>-700.2964282831517</v>
+        <v>-712.5692970398046</v>
       </c>
       <c r="D86">
-        <v>175.7395717168483</v>
+        <v>173.8957029601954</v>
       </c>
       <c r="E86">
-        <v>612.5360000000001</v>
+        <v>622.965</v>
       </c>
       <c r="F86">
-        <v>876.0360000000001</v>
+        <v>886.465</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8467,37 +8467,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M86">
-        <v>206.5692888</v>
+        <v>209.028447</v>
       </c>
       <c r="N86">
-        <v>-161.0359554666667</v>
+        <v>-163.4951136666667</v>
       </c>
       <c r="O86">
-        <v>-48.31078664</v>
+        <v>-49.0485341</v>
       </c>
       <c r="P86">
-        <v>-112.7251688266667</v>
+        <v>-114.4465795666667</v>
       </c>
       <c r="Q86">
-        <v>-51.42516882666668</v>
+        <v>-53.14657956666669</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2500971611866321</v>
+        <v>0.2637169719324075</v>
       </c>
       <c r="T86">
-        <v>4.718179242185498</v>
+        <v>5.032724524997864</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0661279325661308</v>
+        <v>0.06534995688888219</v>
       </c>
       <c r="W86">
-        <v>0.2202070335009064</v>
+        <v>0.2203904801656016</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2204264418871027</v>
+        <v>0.2178331896296073</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2268894539306225</v>
+        <v>0.2287894539306225</v>
       </c>
       <c r="C87">
-        <v>-712.5692970398046</v>
+        <v>-724.8038756047292</v>
       </c>
       <c r="D87">
-        <v>173.8957029601954</v>
+        <v>172.0901243952709</v>
       </c>
       <c r="E87">
-        <v>622.965</v>
+        <v>633.3940000000001</v>
       </c>
       <c r="F87">
-        <v>886.465</v>
+        <v>896.8940000000001</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8549,37 +8549,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M87">
-        <v>209.028447</v>
+        <v>211.4876052</v>
       </c>
       <c r="N87">
-        <v>-163.4951136666667</v>
+        <v>-165.9542718666667</v>
       </c>
       <c r="O87">
-        <v>-49.0485341</v>
+        <v>-49.78628156000001</v>
       </c>
       <c r="P87">
-        <v>-114.4465795666667</v>
+        <v>-116.1679903066667</v>
       </c>
       <c r="Q87">
-        <v>-53.14657956666669</v>
+        <v>-54.8679903066667</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2637169719324075</v>
+        <v>0.2792824699275795</v>
       </c>
       <c r="T87">
-        <v>5.032724524997864</v>
+        <v>5.392204848211998</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06534995688888219</v>
+        <v>0.06459007366924402</v>
       </c>
       <c r="W87">
-        <v>0.2203904801656016</v>
+        <v>0.2205696606287923</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2178331896296073</v>
+        <v>0.2153002455641467</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2287894539306225</v>
+        <v>0.2306894539306225</v>
       </c>
       <c r="C88">
-        <v>-724.8038756047292</v>
+        <v>-737.0013444351565</v>
       </c>
       <c r="D88">
-        <v>172.0901243952709</v>
+        <v>170.3216555648436</v>
       </c>
       <c r="E88">
-        <v>633.3940000000001</v>
+        <v>643.8230000000001</v>
       </c>
       <c r="F88">
-        <v>896.8940000000001</v>
+        <v>907.3230000000001</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8631,37 +8631,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M88">
-        <v>211.4876052</v>
+        <v>213.9467634</v>
       </c>
       <c r="N88">
-        <v>-165.9542718666667</v>
+        <v>-168.4134300666667</v>
       </c>
       <c r="O88">
-        <v>-49.78628156000001</v>
+        <v>-50.52402902000001</v>
       </c>
       <c r="P88">
-        <v>-116.1679903066667</v>
+        <v>-117.8894010466667</v>
       </c>
       <c r="Q88">
-        <v>-54.8679903066667</v>
+        <v>-56.58940104666671</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2792824699275795</v>
+        <v>0.2972426599220087</v>
       </c>
       <c r="T88">
-        <v>5.392204848211998</v>
+        <v>5.806989836535997</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06459007366924402</v>
+        <v>0.06384765902936766</v>
       </c>
       <c r="W88">
-        <v>0.2205696606287923</v>
+        <v>0.2207447220008751</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2153002455641467</v>
+        <v>0.2128255300978922</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2306894539306225</v>
+        <v>0.2325894539306225</v>
       </c>
       <c r="C89">
-        <v>-737.0013444351565</v>
+        <v>-749.162835958438</v>
       </c>
       <c r="D89">
-        <v>170.3216555648436</v>
+        <v>168.5891640415621</v>
       </c>
       <c r="E89">
-        <v>643.8230000000001</v>
+        <v>654.2520000000001</v>
       </c>
       <c r="F89">
-        <v>907.3230000000001</v>
+        <v>917.7520000000001</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8713,37 +8713,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M89">
-        <v>213.9467634</v>
+        <v>216.4059216</v>
       </c>
       <c r="N89">
-        <v>-168.4134300666667</v>
+        <v>-170.8725882666667</v>
       </c>
       <c r="O89">
-        <v>-50.52402902000001</v>
+        <v>-51.26177648000001</v>
       </c>
       <c r="P89">
-        <v>-117.8894010466667</v>
+        <v>-119.6108117866667</v>
       </c>
       <c r="Q89">
-        <v>-56.58940104666671</v>
+        <v>-58.31081178666669</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2972426599220087</v>
+        <v>0.3181962149155095</v>
       </c>
       <c r="T89">
-        <v>5.806989836535997</v>
+        <v>6.290905656247331</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06384765902936766</v>
+        <v>0.06312211744948849</v>
       </c>
       <c r="W89">
-        <v>0.2207447220008751</v>
+        <v>0.2209158047054106</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2128255300978922</v>
+        <v>0.2104070581649616</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2325894539306225</v>
+        <v>0.2344894539306225</v>
       </c>
       <c r="C90">
-        <v>-749.162835958438</v>
+        <v>-761.2894369902198</v>
       </c>
       <c r="D90">
-        <v>168.5891640415621</v>
+        <v>166.8915630097803</v>
       </c>
       <c r="E90">
-        <v>654.2520000000001</v>
+        <v>664.681</v>
       </c>
       <c r="F90">
-        <v>917.7520000000001</v>
+        <v>928.181</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8795,37 +8795,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M90">
-        <v>216.4059216</v>
+        <v>218.8650798</v>
       </c>
       <c r="N90">
-        <v>-170.8725882666667</v>
+        <v>-173.3317464666667</v>
       </c>
       <c r="O90">
-        <v>-51.26177648000001</v>
+        <v>-51.99952394</v>
       </c>
       <c r="P90">
-        <v>-119.6108117866667</v>
+        <v>-121.3322225266667</v>
       </c>
       <c r="Q90">
-        <v>-58.31081178666669</v>
+        <v>-60.03222252666669</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3181962149155095</v>
+        <v>0.3429595071805558</v>
       </c>
       <c r="T90">
-        <v>6.290905656247331</v>
+        <v>6.862806170451634</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06312211744948849</v>
+        <v>0.06241288017477514</v>
       </c>
       <c r="W90">
-        <v>0.2209158047054106</v>
+        <v>0.2210830428547881</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2104070581649616</v>
+        <v>0.2080429339159171</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2344894539306225</v>
+        <v>0.2363894539306225</v>
       </c>
       <c r="C91">
-        <v>-761.2894369902198</v>
+        <v>-773.3821910079737</v>
       </c>
       <c r="D91">
-        <v>166.8915630097803</v>
+        <v>165.2278089920265</v>
       </c>
       <c r="E91">
-        <v>664.681</v>
+        <v>675.1100000000001</v>
       </c>
       <c r="F91">
-        <v>928.181</v>
+        <v>938.6100000000001</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8877,37 +8877,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M91">
-        <v>218.8650798</v>
+        <v>221.324238</v>
       </c>
       <c r="N91">
-        <v>-173.3317464666667</v>
+        <v>-175.7909046666667</v>
       </c>
       <c r="O91">
-        <v>-51.99952394</v>
+        <v>-52.73727140000001</v>
       </c>
       <c r="P91">
-        <v>-121.3322225266667</v>
+        <v>-123.0536332666667</v>
       </c>
       <c r="Q91">
-        <v>-60.03222252666669</v>
+        <v>-61.7536332666667</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3429595071805558</v>
+        <v>0.3726754578986113</v>
       </c>
       <c r="T91">
-        <v>6.862806170451634</v>
+        <v>7.549086787496797</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06241288017477514</v>
+        <v>0.06171940372838874</v>
       </c>
       <c r="W91">
-        <v>0.2210830428547881</v>
+        <v>0.2212465646008459</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2080429339159171</v>
+        <v>0.2057313457612958</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2363894539306225</v>
+        <v>0.2382894539306225</v>
       </c>
       <c r="C92">
-        <v>-773.3821910079737</v>
+        <v>-785.4421002898816</v>
       </c>
       <c r="D92">
-        <v>165.2278089920265</v>
+        <v>163.5968997101184</v>
       </c>
       <c r="E92">
-        <v>675.1100000000001</v>
+        <v>685.5390000000001</v>
       </c>
       <c r="F92">
-        <v>938.6100000000001</v>
+        <v>949.0390000000001</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8959,37 +8959,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M92">
-        <v>221.324238</v>
+        <v>223.7833962</v>
       </c>
       <c r="N92">
-        <v>-175.7909046666667</v>
+        <v>-178.2500628666667</v>
       </c>
       <c r="O92">
-        <v>-52.73727140000001</v>
+        <v>-53.47501886000001</v>
       </c>
       <c r="P92">
-        <v>-123.0536332666667</v>
+        <v>-124.7750440066667</v>
       </c>
       <c r="Q92">
-        <v>-61.7536332666667</v>
+        <v>-63.47504400666669</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3726754578986113</v>
+        <v>0.4089949532206794</v>
       </c>
       <c r="T92">
-        <v>7.549086787496797</v>
+        <v>8.387874208329777</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06171940372838874</v>
+        <v>0.06104116852258228</v>
       </c>
       <c r="W92">
-        <v>0.2212465646008459</v>
+        <v>0.2214064924623751</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2057313457612958</v>
+        <v>0.2034705617419409</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2382894539306225</v>
+        <v>0.2401894539306225</v>
       </c>
       <c r="C93">
-        <v>-785.4421002898816</v>
+        <v>-797.4701279282851</v>
       </c>
       <c r="D93">
-        <v>163.5968997101184</v>
+        <v>161.9978720717149</v>
       </c>
       <c r="E93">
-        <v>685.5390000000001</v>
+        <v>695.9680000000001</v>
       </c>
       <c r="F93">
-        <v>949.0390000000001</v>
+        <v>959.4680000000001</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -9041,37 +9041,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M93">
-        <v>223.7833962</v>
+        <v>226.2425544</v>
       </c>
       <c r="N93">
-        <v>-178.2500628666667</v>
+        <v>-180.7092210666667</v>
       </c>
       <c r="O93">
-        <v>-53.47501886000001</v>
+        <v>-54.21276632000001</v>
       </c>
       <c r="P93">
-        <v>-124.7750440066667</v>
+        <v>-126.4964547466667</v>
       </c>
       <c r="Q93">
-        <v>-63.47504400666669</v>
+        <v>-65.19645474666667</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4089949532206794</v>
+        <v>0.4543943223732644</v>
       </c>
       <c r="T93">
-        <v>8.387874208329777</v>
+        <v>9.436358484371002</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06104116852258228</v>
+        <v>0.06037767756038029</v>
       </c>
       <c r="W93">
-        <v>0.2214064924623751</v>
+        <v>0.2215629436312623</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2034705617419409</v>
+        <v>0.2012589252012676</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2401894539306225</v>
+        <v>0.2420894539306225</v>
       </c>
       <c r="C94">
-        <v>-797.4701279282851</v>
+        <v>-809.4671997261977</v>
       </c>
       <c r="D94">
-        <v>161.9978720717149</v>
+        <v>160.4298002738025</v>
       </c>
       <c r="E94">
-        <v>695.9680000000001</v>
+        <v>706.3970000000002</v>
       </c>
       <c r="F94">
-        <v>959.4680000000001</v>
+        <v>969.8970000000002</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -9123,37 +9123,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M94">
-        <v>226.2425544</v>
+        <v>228.7017126</v>
       </c>
       <c r="N94">
-        <v>-180.7092210666667</v>
+        <v>-183.1683792666667</v>
       </c>
       <c r="O94">
-        <v>-54.21276632000001</v>
+        <v>-54.95051378000001</v>
       </c>
       <c r="P94">
-        <v>-126.4964547466667</v>
+        <v>-128.2178654866667</v>
       </c>
       <c r="Q94">
-        <v>-65.19645474666667</v>
+        <v>-66.91786548666671</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4543943223732644</v>
+        <v>0.5127649398551594</v>
       </c>
       <c r="T94">
-        <v>9.436358484371002</v>
+        <v>10.784409696424</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06037767756038029</v>
+        <v>0.05972845522102136</v>
       </c>
       <c r="W94">
-        <v>0.2215629436312623</v>
+        <v>0.2217160302588832</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2012589252012676</v>
+        <v>0.1990948507367378</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2420894539306225</v>
+        <v>0.2439894539306225</v>
       </c>
       <c r="C95">
-        <v>-809.4671997261977</v>
+        <v>-821.4342059847291</v>
       </c>
       <c r="D95">
-        <v>160.4298002738025</v>
+        <v>158.891794015271</v>
       </c>
       <c r="E95">
-        <v>706.3970000000002</v>
+        <v>716.8260000000001</v>
       </c>
       <c r="F95">
-        <v>969.8970000000002</v>
+        <v>980.3260000000001</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9205,37 +9205,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M95">
-        <v>228.7017126</v>
+        <v>231.1608708000001</v>
       </c>
       <c r="N95">
-        <v>-183.1683792666667</v>
+        <v>-185.6275374666667</v>
       </c>
       <c r="O95">
-        <v>-54.95051378000001</v>
+        <v>-55.68826124000002</v>
       </c>
       <c r="P95">
-        <v>-128.2178654866667</v>
+        <v>-129.9392762266667</v>
       </c>
       <c r="Q95">
-        <v>-66.91786548666671</v>
+        <v>-68.63927622666672</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5127649398551594</v>
+        <v>0.5905924298310193</v>
       </c>
       <c r="T95">
-        <v>10.784409696424</v>
+        <v>12.58181131249467</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05972845522102136</v>
+        <v>0.05909304612292538</v>
       </c>
       <c r="W95">
-        <v>0.2217160302588832</v>
+        <v>0.2218658597242142</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1990948507367378</v>
+        <v>0.1969768204097513</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2439894539306225</v>
+        <v>0.2458894539306225</v>
       </c>
       <c r="C96">
-        <v>-821.4342059847291</v>
+        <v>-833.3720031886721</v>
       </c>
       <c r="D96">
-        <v>158.891794015271</v>
+        <v>157.382996811328</v>
       </c>
       <c r="E96">
-        <v>716.8260000000001</v>
+        <v>727.2550000000001</v>
       </c>
       <c r="F96">
-        <v>980.3260000000001</v>
+        <v>990.7550000000001</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9287,37 +9287,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M96">
-        <v>231.1608708000001</v>
+        <v>233.620029</v>
       </c>
       <c r="N96">
-        <v>-185.6275374666667</v>
+        <v>-188.0866956666667</v>
       </c>
       <c r="O96">
-        <v>-55.68826124000002</v>
+        <v>-56.42600870000001</v>
       </c>
       <c r="P96">
-        <v>-129.9392762266667</v>
+        <v>-131.6606869666667</v>
       </c>
       <c r="Q96">
-        <v>-68.63927622666672</v>
+        <v>-70.36068696666671</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5905924298310193</v>
+        <v>0.6995509157972235</v>
       </c>
       <c r="T96">
-        <v>12.58181131249467</v>
+        <v>15.09817357499361</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05909304612292538</v>
+        <v>0.05847101405847353</v>
       </c>
       <c r="W96">
-        <v>0.2218658597242142</v>
+        <v>0.2220125348850119</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1969768204097513</v>
+        <v>0.1949033801949118</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2458894539306225</v>
+        <v>0.2477894539306225</v>
       </c>
       <c r="C97">
-        <v>-833.3720031886721</v>
+        <v>-845.2814155969569</v>
       </c>
       <c r="D97">
-        <v>157.382996811328</v>
+        <v>155.9025844030433</v>
       </c>
       <c r="E97">
-        <v>727.2550000000001</v>
+        <v>737.6840000000002</v>
       </c>
       <c r="F97">
-        <v>990.7550000000001</v>
+        <v>1001.184</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9369,37 +9369,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M97">
-        <v>233.620029</v>
+        <v>236.0791872000001</v>
       </c>
       <c r="N97">
-        <v>-188.0866956666667</v>
+        <v>-190.5458538666667</v>
       </c>
       <c r="O97">
-        <v>-56.42600870000001</v>
+        <v>-57.16375616000002</v>
       </c>
       <c r="P97">
-        <v>-131.6606869666667</v>
+        <v>-133.3820977066667</v>
       </c>
       <c r="Q97">
-        <v>-70.36068696666671</v>
+        <v>-72.08209770666672</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6995509157972235</v>
+        <v>0.8629886447465298</v>
       </c>
       <c r="T97">
-        <v>15.09817357499361</v>
+        <v>18.87271696874203</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05847101405847353</v>
+        <v>0.05786194099536444</v>
       </c>
       <c r="W97">
-        <v>0.2220125348850119</v>
+        <v>0.2221561543132931</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1949033801949118</v>
+        <v>0.1928731366512147</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2477894539306225</v>
+        <v>0.2496894539306225</v>
       </c>
       <c r="C98">
-        <v>-845.2814155969568</v>
+        <v>-857.1632367441779</v>
       </c>
       <c r="D98">
-        <v>155.9025844030433</v>
+        <v>154.4497632558222</v>
       </c>
       <c r="E98">
-        <v>737.6840000000001</v>
+        <v>748.1130000000001</v>
       </c>
       <c r="F98">
-        <v>1001.184</v>
+        <v>1011.613</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9451,37 +9451,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M98">
-        <v>236.0791872</v>
+        <v>238.5383454</v>
       </c>
       <c r="N98">
-        <v>-190.5458538666667</v>
+        <v>-193.0050120666667</v>
       </c>
       <c r="O98">
-        <v>-57.16375616000001</v>
+        <v>-57.90150362000001</v>
       </c>
       <c r="P98">
-        <v>-133.3820977066667</v>
+        <v>-135.1035084466667</v>
       </c>
       <c r="Q98">
-        <v>-72.08209770666669</v>
+        <v>-73.8035084466667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8629886447465276</v>
+        <v>1.135384859662037</v>
       </c>
       <c r="T98">
-        <v>18.87271696874198</v>
+        <v>25.1636226249893</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05786194099536444</v>
+        <v>0.05726542613974213</v>
       </c>
       <c r="W98">
-        <v>0.2221561543132931</v>
+        <v>0.2222968125162488</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1928731366512149</v>
+        <v>0.1908847537991405</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2496894539306225</v>
+        <v>0.2515894539306225</v>
       </c>
       <c r="C99">
-        <v>-857.1632367441779</v>
+        <v>-869.0182308589443</v>
       </c>
       <c r="D99">
-        <v>154.4497632558222</v>
+        <v>153.0237691410557</v>
       </c>
       <c r="E99">
-        <v>748.1130000000001</v>
+        <v>758.542</v>
       </c>
       <c r="F99">
-        <v>1011.613</v>
+        <v>1022.042</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9533,37 +9533,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M99">
-        <v>238.5383454</v>
+        <v>240.9975036</v>
       </c>
       <c r="N99">
-        <v>-193.0050120666667</v>
+        <v>-195.4641702666667</v>
       </c>
       <c r="O99">
-        <v>-57.90150362000001</v>
+        <v>-58.63925108</v>
       </c>
       <c r="P99">
-        <v>-135.1035084466667</v>
+        <v>-136.8249191866667</v>
       </c>
       <c r="Q99">
-        <v>-73.8035084466667</v>
+        <v>-75.52491918666668</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.135384859662037</v>
+        <v>1.680177289493055</v>
       </c>
       <c r="T99">
-        <v>25.1636226249893</v>
+        <v>37.74543393748395</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05726542613974213</v>
+        <v>0.05668108505668355</v>
       </c>
       <c r="W99">
-        <v>0.2222968125162488</v>
+        <v>0.222434600143634</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1908847537991405</v>
+        <v>0.1889369501889452</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2515894539306225</v>
+        <v>0.2534894539306225</v>
       </c>
       <c r="C100">
-        <v>-869.0182308589443</v>
+        <v>-880.8471342043742</v>
       </c>
       <c r="D100">
-        <v>153.0237691410557</v>
+        <v>151.6238657956258</v>
       </c>
       <c r="E100">
-        <v>758.542</v>
+        <v>768.971</v>
       </c>
       <c r="F100">
-        <v>1022.042</v>
+        <v>1032.471</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9615,37 +9615,37 @@
         <v>45.53333333333333</v>
       </c>
       <c r="M100">
-        <v>240.9975036</v>
+        <v>243.4566618</v>
       </c>
       <c r="N100">
-        <v>-195.4641702666667</v>
+        <v>-197.9233284666667</v>
       </c>
       <c r="O100">
-        <v>-58.63925108</v>
+        <v>-59.37699854</v>
       </c>
       <c r="P100">
-        <v>-136.8249191866667</v>
+        <v>-138.5463299266667</v>
       </c>
       <c r="Q100">
-        <v>-75.52491918666668</v>
+        <v>-77.24632992666666</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.680177289493055</v>
+        <v>3.31455457898611</v>
       </c>
       <c r="T100">
-        <v>37.74543393748395</v>
+        <v>75.4908678749679</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05668108505668355</v>
+        <v>0.05610854884398978</v>
       </c>
       <c r="W100">
-        <v>0.222434600143634</v>
+        <v>0.2225696041825872</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1889369501889452</v>
+        <v>0.1870284961466325</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2534894539306225</v>
-      </c>
-      <c r="C101">
-        <v>-880.8471342043742</v>
-      </c>
-      <c r="D101">
-        <v>151.6238657956258</v>
-      </c>
-      <c r="E101">
-        <v>768.971</v>
-      </c>
-      <c r="F101">
-        <v>1032.471</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>779.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>106.8333333333333</v>
-      </c>
-      <c r="K101">
-        <v>61.3</v>
-      </c>
-      <c r="L101">
-        <v>45.53333333333333</v>
-      </c>
-      <c r="M101">
-        <v>243.4566618</v>
-      </c>
-      <c r="N101">
-        <v>-197.9233284666667</v>
-      </c>
-      <c r="O101">
-        <v>-59.37699854</v>
-      </c>
-      <c r="P101">
-        <v>-138.5463299266667</v>
-      </c>
-      <c r="Q101">
-        <v>-77.24632992666666</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.31455457898611</v>
-      </c>
-      <c r="T101">
-        <v>75.4908678749679</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05610854884398978</v>
-      </c>
-      <c r="W101">
-        <v>0.2225696041825872</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1870284961466325</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
